--- a/Australia/data_raw/560101.xlsx
+++ b/Australia/data_raw/560101.xlsx
@@ -17,98 +17,98 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A130267829X">Data1!$K$1:$K$10,Data1!$K$11:$K$104</definedName>
-    <definedName name="A130267829X_Data">Data1!$K$11:$K$104</definedName>
-    <definedName name="A130267829X_Latest">Data1!$K$104</definedName>
-    <definedName name="A130267830J">Data1!$F$1:$F$10,Data1!$F$11:$F$104</definedName>
-    <definedName name="A130267830J_Data">Data1!$F$11:$F$104</definedName>
-    <definedName name="A130267830J_Latest">Data1!$F$104</definedName>
-    <definedName name="A130268023F">Data1!$T$1:$T$10,Data1!$T$11:$T$104</definedName>
-    <definedName name="A130268023F_Data">Data1!$T$11:$T$104</definedName>
-    <definedName name="A130268023F_Latest">Data1!$T$104</definedName>
-    <definedName name="A130268024J">Data1!$O$1:$O$10,Data1!$O$11:$O$104</definedName>
-    <definedName name="A130268024J_Data">Data1!$O$11:$O$104</definedName>
-    <definedName name="A130268024J_Latest">Data1!$O$104</definedName>
-    <definedName name="A130268135X">Data1!$J$1:$J$10,Data1!$J$11:$J$104</definedName>
-    <definedName name="A130268135X_Data">Data1!$J$11:$J$104</definedName>
-    <definedName name="A130268135X_Latest">Data1!$J$104</definedName>
-    <definedName name="A130268136A">Data1!$E$1:$E$10,Data1!$E$11:$E$104</definedName>
-    <definedName name="A130268136A_Data">Data1!$E$11:$E$104</definedName>
-    <definedName name="A130268136A_Latest">Data1!$E$104</definedName>
-    <definedName name="A130268206W">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$104</definedName>
-    <definedName name="A130268206W_Data">Data1!$AA$11:$AA$104</definedName>
-    <definedName name="A130268206W_Latest">Data1!$AA$104</definedName>
-    <definedName name="A130268207X">Data1!$V$1:$V$10,Data1!$V$79:$V$104</definedName>
-    <definedName name="A130268207X_Data">Data1!$V$79:$V$104</definedName>
-    <definedName name="A130268207X_Latest">Data1!$V$104</definedName>
-    <definedName name="A130268269F">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$104</definedName>
-    <definedName name="A130268269F_Data">Data1!$AE$11:$AE$104</definedName>
-    <definedName name="A130268269F_Latest">Data1!$AE$104</definedName>
-    <definedName name="A130268270R">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$104</definedName>
-    <definedName name="A130268270R_Data">Data1!$Z$11:$Z$104</definedName>
-    <definedName name="A130268270R_Latest">Data1!$Z$104</definedName>
-    <definedName name="A130268362X">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$104</definedName>
-    <definedName name="A130268362X_Data">Data1!$AC$11:$AC$104</definedName>
-    <definedName name="A130268362X_Latest">Data1!$AC$104</definedName>
-    <definedName name="A130268363A">Data1!$X$1:$X$10,Data1!$X$79:$X$104</definedName>
-    <definedName name="A130268363A_Data">Data1!$X$79:$X$104</definedName>
-    <definedName name="A130268363A_Latest">Data1!$X$104</definedName>
-    <definedName name="A130268471K">Data1!$I$1:$I$10,Data1!$I$11:$I$104</definedName>
-    <definedName name="A130268471K_Data">Data1!$I$11:$I$104</definedName>
-    <definedName name="A130268471K_Latest">Data1!$I$104</definedName>
-    <definedName name="A130268472L">Data1!$D$1:$D$10,Data1!$D$79:$D$104</definedName>
-    <definedName name="A130268472L_Data">Data1!$D$79:$D$104</definedName>
-    <definedName name="A130268472L_Latest">Data1!$D$104</definedName>
-    <definedName name="A130268483V">Data1!$U$1:$U$10,Data1!$U$11:$U$104</definedName>
-    <definedName name="A130268483V_Data">Data1!$U$11:$U$104</definedName>
-    <definedName name="A130268483V_Latest">Data1!$U$104</definedName>
-    <definedName name="A130268484W">Data1!$P$1:$P$10,Data1!$P$11:$P$104</definedName>
-    <definedName name="A130268484W_Data">Data1!$P$11:$P$104</definedName>
-    <definedName name="A130268484W_Latest">Data1!$P$104</definedName>
-    <definedName name="A130268494A">Data1!$S$1:$S$10,Data1!$S$11:$S$104</definedName>
-    <definedName name="A130268494A_Data">Data1!$S$11:$S$104</definedName>
-    <definedName name="A130268494A_Latest">Data1!$S$104</definedName>
-    <definedName name="A130268495C">Data1!$N$1:$N$10,Data1!$N$79:$N$104</definedName>
-    <definedName name="A130268495C_Data">Data1!$N$79:$N$104</definedName>
-    <definedName name="A130268495C_Latest">Data1!$N$104</definedName>
-    <definedName name="A130268636W">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$104</definedName>
-    <definedName name="A130268636W_Data">Data1!$AD$11:$AD$104</definedName>
-    <definedName name="A130268636W_Latest">Data1!$AD$104</definedName>
-    <definedName name="A130268637X">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$104</definedName>
-    <definedName name="A130268637X_Data">Data1!$Y$11:$Y$104</definedName>
-    <definedName name="A130268637X_Latest">Data1!$Y$104</definedName>
-    <definedName name="A130268676R">Data1!$G$1:$G$10,Data1!$G$11:$G$104</definedName>
-    <definedName name="A130268676R_Data">Data1!$G$11:$G$104</definedName>
-    <definedName name="A130268676R_Latest">Data1!$G$104</definedName>
-    <definedName name="A130268677T">Data1!$B$1:$B$10,Data1!$B$79:$B$104</definedName>
-    <definedName name="A130268677T_Data">Data1!$B$79:$B$104</definedName>
-    <definedName name="A130268677T_Latest">Data1!$B$104</definedName>
-    <definedName name="A130268858C">Data1!$H$1:$H$10,Data1!$H$11:$H$104</definedName>
-    <definedName name="A130268858C_Data">Data1!$H$11:$H$104</definedName>
-    <definedName name="A130268858C_Latest">Data1!$H$104</definedName>
-    <definedName name="A130268859F">Data1!$C$1:$C$10,Data1!$C$11:$C$104</definedName>
-    <definedName name="A130268859F_Data">Data1!$C$11:$C$104</definedName>
-    <definedName name="A130268859F_Latest">Data1!$C$104</definedName>
-    <definedName name="A130268885K">Data1!$R$1:$R$10,Data1!$R$11:$R$104</definedName>
-    <definedName name="A130268885K_Data">Data1!$R$11:$R$104</definedName>
-    <definedName name="A130268885K_Latest">Data1!$R$104</definedName>
-    <definedName name="A130268886L">Data1!$M$1:$M$10,Data1!$M$11:$M$104</definedName>
-    <definedName name="A130268886L_Data">Data1!$M$11:$M$104</definedName>
-    <definedName name="A130268886L_Latest">Data1!$M$104</definedName>
-    <definedName name="A130268891F">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$104</definedName>
-    <definedName name="A130268891F_Data">Data1!$Q$11:$Q$104</definedName>
-    <definedName name="A130268891F_Latest">Data1!$Q$104</definedName>
-    <definedName name="A130268892J">Data1!$L$1:$L$10,Data1!$L$79:$L$104</definedName>
-    <definedName name="A130268892J_Data">Data1!$L$79:$L$104</definedName>
-    <definedName name="A130268892J_Latest">Data1!$L$104</definedName>
-    <definedName name="A130268903C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$104</definedName>
-    <definedName name="A130268903C_Data">Data1!$AB$11:$AB$104</definedName>
-    <definedName name="A130268903C_Latest">Data1!$AB$104</definedName>
-    <definedName name="A130268904F">Data1!$W$1:$W$10,Data1!$W$11:$W$104</definedName>
-    <definedName name="A130268904F_Data">Data1!$W$11:$W$104</definedName>
-    <definedName name="A130268904F_Latest">Data1!$W$104</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$104</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$104</definedName>
+    <definedName name="A130267829X">Data1!$K$1:$K$10,Data1!$K$11:$K$105</definedName>
+    <definedName name="A130267829X_Data">Data1!$K$11:$K$105</definedName>
+    <definedName name="A130267829X_Latest">Data1!$K$105</definedName>
+    <definedName name="A130267830J">Data1!$F$1:$F$10,Data1!$F$11:$F$105</definedName>
+    <definedName name="A130267830J_Data">Data1!$F$11:$F$105</definedName>
+    <definedName name="A130267830J_Latest">Data1!$F$105</definedName>
+    <definedName name="A130268023F">Data1!$T$1:$T$10,Data1!$T$11:$T$105</definedName>
+    <definedName name="A130268023F_Data">Data1!$T$11:$T$105</definedName>
+    <definedName name="A130268023F_Latest">Data1!$T$105</definedName>
+    <definedName name="A130268024J">Data1!$O$1:$O$10,Data1!$O$11:$O$105</definedName>
+    <definedName name="A130268024J_Data">Data1!$O$11:$O$105</definedName>
+    <definedName name="A130268024J_Latest">Data1!$O$105</definedName>
+    <definedName name="A130268135X">Data1!$J$1:$J$10,Data1!$J$11:$J$105</definedName>
+    <definedName name="A130268135X_Data">Data1!$J$11:$J$105</definedName>
+    <definedName name="A130268135X_Latest">Data1!$J$105</definedName>
+    <definedName name="A130268136A">Data1!$E$1:$E$10,Data1!$E$11:$E$105</definedName>
+    <definedName name="A130268136A_Data">Data1!$E$11:$E$105</definedName>
+    <definedName name="A130268136A_Latest">Data1!$E$105</definedName>
+    <definedName name="A130268206W">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$105</definedName>
+    <definedName name="A130268206W_Data">Data1!$AA$11:$AA$105</definedName>
+    <definedName name="A130268206W_Latest">Data1!$AA$105</definedName>
+    <definedName name="A130268207X">Data1!$V$1:$V$10,Data1!$V$79:$V$105</definedName>
+    <definedName name="A130268207X_Data">Data1!$V$79:$V$105</definedName>
+    <definedName name="A130268207X_Latest">Data1!$V$105</definedName>
+    <definedName name="A130268269F">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$105</definedName>
+    <definedName name="A130268269F_Data">Data1!$AE$11:$AE$105</definedName>
+    <definedName name="A130268269F_Latest">Data1!$AE$105</definedName>
+    <definedName name="A130268270R">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$105</definedName>
+    <definedName name="A130268270R_Data">Data1!$Z$11:$Z$105</definedName>
+    <definedName name="A130268270R_Latest">Data1!$Z$105</definedName>
+    <definedName name="A130268362X">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$105</definedName>
+    <definedName name="A130268362X_Data">Data1!$AC$11:$AC$105</definedName>
+    <definedName name="A130268362X_Latest">Data1!$AC$105</definedName>
+    <definedName name="A130268363A">Data1!$X$1:$X$10,Data1!$X$79:$X$105</definedName>
+    <definedName name="A130268363A_Data">Data1!$X$79:$X$105</definedName>
+    <definedName name="A130268363A_Latest">Data1!$X$105</definedName>
+    <definedName name="A130268471K">Data1!$I$1:$I$10,Data1!$I$11:$I$105</definedName>
+    <definedName name="A130268471K_Data">Data1!$I$11:$I$105</definedName>
+    <definedName name="A130268471K_Latest">Data1!$I$105</definedName>
+    <definedName name="A130268472L">Data1!$D$1:$D$10,Data1!$D$79:$D$105</definedName>
+    <definedName name="A130268472L_Data">Data1!$D$79:$D$105</definedName>
+    <definedName name="A130268472L_Latest">Data1!$D$105</definedName>
+    <definedName name="A130268483V">Data1!$U$1:$U$10,Data1!$U$11:$U$105</definedName>
+    <definedName name="A130268483V_Data">Data1!$U$11:$U$105</definedName>
+    <definedName name="A130268483V_Latest">Data1!$U$105</definedName>
+    <definedName name="A130268484W">Data1!$P$1:$P$10,Data1!$P$11:$P$105</definedName>
+    <definedName name="A130268484W_Data">Data1!$P$11:$P$105</definedName>
+    <definedName name="A130268484W_Latest">Data1!$P$105</definedName>
+    <definedName name="A130268494A">Data1!$S$1:$S$10,Data1!$S$11:$S$105</definedName>
+    <definedName name="A130268494A_Data">Data1!$S$11:$S$105</definedName>
+    <definedName name="A130268494A_Latest">Data1!$S$105</definedName>
+    <definedName name="A130268495C">Data1!$N$1:$N$10,Data1!$N$79:$N$105</definedName>
+    <definedName name="A130268495C_Data">Data1!$N$79:$N$105</definedName>
+    <definedName name="A130268495C_Latest">Data1!$N$105</definedName>
+    <definedName name="A130268636W">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$105</definedName>
+    <definedName name="A130268636W_Data">Data1!$AD$11:$AD$105</definedName>
+    <definedName name="A130268636W_Latest">Data1!$AD$105</definedName>
+    <definedName name="A130268637X">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$105</definedName>
+    <definedName name="A130268637X_Data">Data1!$Y$11:$Y$105</definedName>
+    <definedName name="A130268637X_Latest">Data1!$Y$105</definedName>
+    <definedName name="A130268676R">Data1!$G$1:$G$10,Data1!$G$11:$G$105</definedName>
+    <definedName name="A130268676R_Data">Data1!$G$11:$G$105</definedName>
+    <definedName name="A130268676R_Latest">Data1!$G$105</definedName>
+    <definedName name="A130268677T">Data1!$B$1:$B$10,Data1!$B$79:$B$105</definedName>
+    <definedName name="A130268677T_Data">Data1!$B$79:$B$105</definedName>
+    <definedName name="A130268677T_Latest">Data1!$B$105</definedName>
+    <definedName name="A130268858C">Data1!$H$1:$H$10,Data1!$H$11:$H$105</definedName>
+    <definedName name="A130268858C_Data">Data1!$H$11:$H$105</definedName>
+    <definedName name="A130268858C_Latest">Data1!$H$105</definedName>
+    <definedName name="A130268859F">Data1!$C$1:$C$10,Data1!$C$11:$C$105</definedName>
+    <definedName name="A130268859F_Data">Data1!$C$11:$C$105</definedName>
+    <definedName name="A130268859F_Latest">Data1!$C$105</definedName>
+    <definedName name="A130268885K">Data1!$R$1:$R$10,Data1!$R$11:$R$105</definedName>
+    <definedName name="A130268885K_Data">Data1!$R$11:$R$105</definedName>
+    <definedName name="A130268885K_Latest">Data1!$R$105</definedName>
+    <definedName name="A130268886L">Data1!$M$1:$M$10,Data1!$M$11:$M$105</definedName>
+    <definedName name="A130268886L_Data">Data1!$M$11:$M$105</definedName>
+    <definedName name="A130268886L_Latest">Data1!$M$105</definedName>
+    <definedName name="A130268891F">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$105</definedName>
+    <definedName name="A130268891F_Data">Data1!$Q$11:$Q$105</definedName>
+    <definedName name="A130268891F_Latest">Data1!$Q$105</definedName>
+    <definedName name="A130268892J">Data1!$L$1:$L$10,Data1!$L$79:$L$105</definedName>
+    <definedName name="A130268892J_Data">Data1!$L$79:$L$105</definedName>
+    <definedName name="A130268892J_Latest">Data1!$L$105</definedName>
+    <definedName name="A130268903C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$105</definedName>
+    <definedName name="A130268903C_Data">Data1!$AB$11:$AB$105</definedName>
+    <definedName name="A130268903C_Latest">Data1!$AB$105</definedName>
+    <definedName name="A130268904F">Data1!$W$1:$W$10,Data1!$W$11:$W$105</definedName>
+    <definedName name="A130268904F_Data">Data1!$W$11:$W$105</definedName>
+    <definedName name="A130268904F_Latest">Data1!$W$105</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$105</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$105</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1048,10 +1048,10 @@
         <v>43709</v>
       </c>
       <c r="G12" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H12" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>19</v>
@@ -1080,10 +1080,10 @@
         <v>37500</v>
       </c>
       <c r="G13" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H13" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>19</v>
@@ -1112,10 +1112,10 @@
         <v>43709</v>
       </c>
       <c r="G14" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H14" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>19</v>
@@ -1144,10 +1144,10 @@
         <v>37500</v>
       </c>
       <c r="G15" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H15" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>19</v>
@@ -1176,10 +1176,10 @@
         <v>37500</v>
       </c>
       <c r="G16" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H16" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>19</v>
@@ -1208,10 +1208,10 @@
         <v>37500</v>
       </c>
       <c r="G17" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H17" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>28</v>
@@ -1240,10 +1240,10 @@
         <v>37500</v>
       </c>
       <c r="G18" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H18" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>28</v>
@@ -1272,10 +1272,10 @@
         <v>37500</v>
       </c>
       <c r="G19" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H19" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>28</v>
@@ -1304,10 +1304,10 @@
         <v>37500</v>
       </c>
       <c r="G20" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H20" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>28</v>
@@ -1336,10 +1336,10 @@
         <v>37500</v>
       </c>
       <c r="G21" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H21" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>28</v>
@@ -1368,10 +1368,10 @@
         <v>43709</v>
       </c>
       <c r="G22" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H22" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>19</v>
@@ -1400,10 +1400,10 @@
         <v>37500</v>
       </c>
       <c r="G23" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H23" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>19</v>
@@ -1432,10 +1432,10 @@
         <v>43709</v>
       </c>
       <c r="G24" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H24" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>19</v>
@@ -1464,10 +1464,10 @@
         <v>37500</v>
       </c>
       <c r="G25" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H25" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>19</v>
@@ -1496,10 +1496,10 @@
         <v>37500</v>
       </c>
       <c r="G26" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H26" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>19</v>
@@ -1528,10 +1528,10 @@
         <v>37500</v>
       </c>
       <c r="G27" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H27" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>28</v>
@@ -1560,10 +1560,10 @@
         <v>37500</v>
       </c>
       <c r="G28" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H28" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>28</v>
@@ -1592,10 +1592,10 @@
         <v>37500</v>
       </c>
       <c r="G29" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H29" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>28</v>
@@ -1624,10 +1624,10 @@
         <v>37500</v>
       </c>
       <c r="G30" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H30" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>28</v>
@@ -1656,10 +1656,10 @@
         <v>37500</v>
       </c>
       <c r="G31" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H31" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>28</v>
@@ -1688,10 +1688,10 @@
         <v>43709</v>
       </c>
       <c r="G32" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H32" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>19</v>
@@ -1720,10 +1720,10 @@
         <v>37500</v>
       </c>
       <c r="G33" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H33" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>19</v>
@@ -1752,10 +1752,10 @@
         <v>43709</v>
       </c>
       <c r="G34" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H34" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>19</v>
@@ -1784,10 +1784,10 @@
         <v>37500</v>
       </c>
       <c r="G35" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H35" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>19</v>
@@ -1816,10 +1816,10 @@
         <v>37500</v>
       </c>
       <c r="G36" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H36" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>19</v>
@@ -1848,10 +1848,10 @@
         <v>37500</v>
       </c>
       <c r="G37" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H37" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>28</v>
@@ -1880,10 +1880,10 @@
         <v>37500</v>
       </c>
       <c r="G38" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H38" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>28</v>
@@ -1912,10 +1912,10 @@
         <v>37500</v>
       </c>
       <c r="G39" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H39" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>28</v>
@@ -1944,10 +1944,10 @@
         <v>37500</v>
       </c>
       <c r="G40" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H40" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>28</v>
@@ -1976,10 +1976,10 @@
         <v>37500</v>
       </c>
       <c r="G41" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H41" s="11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>28</v>
@@ -2044,7 +2044,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE104"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -2717,94 +2717,94 @@
         <v>16</v>
       </c>
       <c r="B8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="D8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="F8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="G8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="I8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="J8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="K8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="L8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="M8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="N8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="O8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="P8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Q8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="R8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="S8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="T8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="U8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="V8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="W8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="X8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Y8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Z8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AA8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AB8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AC8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AD8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AE8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
@@ -2812,94 +2812,94 @@
         <v>17</v>
       </c>
       <c r="B9" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L9" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N9" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="V9" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X9" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Z9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AB9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AD9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AE9" s="1">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
@@ -3139,7 +3139,7 @@
         <v>28680</v>
       </c>
       <c r="AB12" s="9">
-        <v>17446.400000000001</v>
+        <v>17446.3</v>
       </c>
       <c r="AC12" s="9">
         <v>11233.7</v>
@@ -3420,7 +3420,7 @@
         <v>21147</v>
       </c>
       <c r="Q16" s="9">
-        <v>37187.4</v>
+        <v>37187.300000000003</v>
       </c>
       <c r="R16" s="9">
         <v>20909.8</v>
@@ -4732,7 +4732,7 @@
         <v>42412.800000000003</v>
       </c>
       <c r="R33" s="9">
-        <v>26756.9</v>
+        <v>26756.799999999999</v>
       </c>
       <c r="S33" s="9">
         <v>15656</v>
@@ -5037,10 +5037,10 @@
         <v>44768</v>
       </c>
       <c r="Q37" s="9">
-        <v>42863</v>
+        <v>42862.9</v>
       </c>
       <c r="R37" s="9">
-        <v>30092.3</v>
+        <v>30092.2</v>
       </c>
       <c r="S37" s="9">
         <v>12770.7</v>
@@ -5117,7 +5117,7 @@
         <v>46289.5</v>
       </c>
       <c r="R38" s="9">
-        <v>32399.8</v>
+        <v>32399.7</v>
       </c>
       <c r="S38" s="9">
         <v>13889.8</v>
@@ -5147,7 +5147,7 @@
         <v>14006.4</v>
       </c>
       <c r="AD38" s="9">
-        <v>17711.599999999999</v>
+        <v>17711.7</v>
       </c>
       <c r="AE38" s="9">
         <v>14495.1</v>
@@ -5191,10 +5191,10 @@
         <v>44295</v>
       </c>
       <c r="Q39" s="9">
-        <v>48156.800000000003</v>
+        <v>48156.9</v>
       </c>
       <c r="R39" s="9">
-        <v>32609.8</v>
+        <v>32609.9</v>
       </c>
       <c r="S39" s="9">
         <v>15547</v>
@@ -5218,7 +5218,7 @@
         <v>47560.2</v>
       </c>
       <c r="AB39" s="9">
-        <v>32363.599999999999</v>
+        <v>32363.7</v>
       </c>
       <c r="AC39" s="9">
         <v>15196.5</v>
@@ -5271,7 +5271,7 @@
         <v>46365.8</v>
       </c>
       <c r="R40" s="9">
-        <v>30403.5</v>
+        <v>30403.599999999999</v>
       </c>
       <c r="S40" s="9">
         <v>15962.2</v>
@@ -5292,16 +5292,16 @@
         <v>34971</v>
       </c>
       <c r="AA40" s="9">
-        <v>46278.1</v>
+        <v>46278</v>
       </c>
       <c r="AB40" s="9">
-        <v>30201.200000000001</v>
+        <v>30201.1</v>
       </c>
       <c r="AC40" s="9">
         <v>16076.9</v>
       </c>
       <c r="AD40" s="9">
-        <v>19491</v>
+        <v>19490.900000000001</v>
       </c>
       <c r="AE40" s="9">
         <v>10807.6</v>
@@ -5345,10 +5345,10 @@
         <v>25100</v>
       </c>
       <c r="Q41" s="9">
-        <v>43385.8</v>
+        <v>43385.7</v>
       </c>
       <c r="R41" s="9">
-        <v>27059.3</v>
+        <v>27059.200000000001</v>
       </c>
       <c r="S41" s="9">
         <v>16326.6</v>
@@ -5369,7 +5369,7 @@
         <v>26380</v>
       </c>
       <c r="AA41" s="9">
-        <v>43900.4</v>
+        <v>43900.3</v>
       </c>
       <c r="AB41" s="9">
         <v>27562.1</v>
@@ -5422,10 +5422,10 @@
         <v>20955</v>
       </c>
       <c r="Q42" s="9">
-        <v>41748.5</v>
+        <v>41748.300000000003</v>
       </c>
       <c r="R42" s="9">
-        <v>25395.7</v>
+        <v>25395.599999999999</v>
       </c>
       <c r="S42" s="9">
         <v>16352.8</v>
@@ -5455,7 +5455,7 @@
         <v>16112</v>
       </c>
       <c r="AD42" s="9">
-        <v>19060.3</v>
+        <v>19060.400000000001</v>
       </c>
       <c r="AE42" s="9">
         <v>6830</v>
@@ -5499,10 +5499,10 @@
         <v>20281</v>
       </c>
       <c r="Q43" s="9">
-        <v>40724</v>
+        <v>40724.300000000003</v>
       </c>
       <c r="R43" s="9">
-        <v>25458.6</v>
+        <v>25458.9</v>
       </c>
       <c r="S43" s="9">
         <v>15265.4</v>
@@ -5523,10 +5523,10 @@
         <v>19801</v>
       </c>
       <c r="AA43" s="9">
-        <v>40792.5</v>
+        <v>40792.6</v>
       </c>
       <c r="AB43" s="9">
-        <v>25246.1</v>
+        <v>25246.2</v>
       </c>
       <c r="AC43" s="9">
         <v>15546.4</v>
@@ -5535,7 +5535,7 @@
         <v>19025.099999999999</v>
       </c>
       <c r="AE43" s="9">
-        <v>6283.2</v>
+        <v>6283.3</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.2">
@@ -5576,13 +5576,13 @@
         <v>20017</v>
       </c>
       <c r="Q44" s="9">
-        <v>40545.199999999997</v>
+        <v>40545.300000000003</v>
       </c>
       <c r="R44" s="9">
         <v>25511.7</v>
       </c>
       <c r="S44" s="9">
-        <v>15033.5</v>
+        <v>15033.6</v>
       </c>
       <c r="T44" s="9">
         <v>19396.400000000001</v>
@@ -5603,7 +5603,7 @@
         <v>39905.4</v>
       </c>
       <c r="AB44" s="9">
-        <v>25134.1</v>
+        <v>25134</v>
       </c>
       <c r="AC44" s="9">
         <v>14771.4</v>
@@ -5653,10 +5653,10 @@
         <v>19497</v>
       </c>
       <c r="Q45" s="9">
-        <v>38589.199999999997</v>
+        <v>38589</v>
       </c>
       <c r="R45" s="9">
-        <v>24610</v>
+        <v>24609.9</v>
       </c>
       <c r="S45" s="9">
         <v>13979.2</v>
@@ -5677,10 +5677,10 @@
         <v>19630</v>
       </c>
       <c r="AA45" s="9">
-        <v>39154</v>
+        <v>39153.800000000003</v>
       </c>
       <c r="AB45" s="9">
-        <v>24952</v>
+        <v>24951.9</v>
       </c>
       <c r="AC45" s="9">
         <v>14201.9</v>
@@ -5730,10 +5730,10 @@
         <v>20224</v>
       </c>
       <c r="Q46" s="9">
-        <v>38672.300000000003</v>
+        <v>38671.9</v>
       </c>
       <c r="R46" s="9">
-        <v>24835.1</v>
+        <v>24834.7</v>
       </c>
       <c r="S46" s="9">
         <v>13837.3</v>
@@ -5742,7 +5742,7 @@
         <v>18468.099999999999</v>
       </c>
       <c r="U46" s="9">
-        <v>6396.2</v>
+        <v>6396.1</v>
       </c>
       <c r="W46" s="8">
         <v>68717</v>
@@ -5754,7 +5754,7 @@
         <v>20299</v>
       </c>
       <c r="AA46" s="9">
-        <v>38646.5</v>
+        <v>38646.400000000001</v>
       </c>
       <c r="AB46" s="9">
         <v>24751.5</v>
@@ -5807,19 +5807,19 @@
         <v>21071</v>
       </c>
       <c r="Q47" s="9">
-        <v>39040.6</v>
+        <v>39041.199999999997</v>
       </c>
       <c r="R47" s="9">
-        <v>24826.6</v>
+        <v>24827.200000000001</v>
       </c>
       <c r="S47" s="9">
         <v>14214</v>
       </c>
       <c r="T47" s="9">
-        <v>18205.099999999999</v>
+        <v>18205.2</v>
       </c>
       <c r="U47" s="9">
-        <v>6698.9</v>
+        <v>6699</v>
       </c>
       <c r="W47" s="8">
         <v>69575</v>
@@ -5831,10 +5831,10 @@
         <v>21816</v>
       </c>
       <c r="AA47" s="9">
-        <v>38713.9</v>
+        <v>38714.1</v>
       </c>
       <c r="AB47" s="9">
-        <v>24742.799999999999</v>
+        <v>24742.9</v>
       </c>
       <c r="AC47" s="9">
         <v>13971.1</v>
@@ -5878,19 +5878,19 @@
         <v>71069</v>
       </c>
       <c r="O48" s="8">
-        <v>46571</v>
+        <v>46570</v>
       </c>
       <c r="P48" s="8">
         <v>24368</v>
       </c>
       <c r="Q48" s="9">
-        <v>38597.599999999999</v>
+        <v>38597.800000000003</v>
       </c>
       <c r="R48" s="9">
-        <v>24701</v>
+        <v>24701.200000000001</v>
       </c>
       <c r="S48" s="9">
-        <v>13896.6</v>
+        <v>13896.7</v>
       </c>
       <c r="T48" s="9">
         <v>17076</v>
@@ -5961,19 +5961,19 @@
         <v>23423</v>
       </c>
       <c r="Q49" s="9">
-        <v>40285.1</v>
+        <v>40284.5</v>
       </c>
       <c r="R49" s="9">
-        <v>25008.2</v>
+        <v>25007.599999999999</v>
       </c>
       <c r="S49" s="9">
         <v>15276.9</v>
       </c>
       <c r="T49" s="9">
-        <v>17630.3</v>
+        <v>17630.2</v>
       </c>
       <c r="U49" s="9">
-        <v>7309.5</v>
+        <v>7309.4</v>
       </c>
       <c r="W49" s="8">
         <v>71329</v>
@@ -5985,10 +5985,10 @@
         <v>23583</v>
       </c>
       <c r="AA49" s="9">
-        <v>39632.199999999997</v>
+        <v>39632</v>
       </c>
       <c r="AB49" s="9">
-        <v>24886</v>
+        <v>24885.8</v>
       </c>
       <c r="AC49" s="9">
         <v>14746.2</v>
@@ -6029,7 +6029,7 @@
         <v>7163.6</v>
       </c>
       <c r="M50" s="8">
-        <v>70809</v>
+        <v>70810</v>
       </c>
       <c r="O50" s="8">
         <v>48054</v>
@@ -6038,10 +6038,10 @@
         <v>22465</v>
       </c>
       <c r="Q50" s="9">
-        <v>39834.800000000003</v>
+        <v>39834.300000000003</v>
       </c>
       <c r="R50" s="9">
-        <v>24947.7</v>
+        <v>24947.3</v>
       </c>
       <c r="S50" s="9">
         <v>14887</v>
@@ -6065,13 +6065,13 @@
         <v>40089.9</v>
       </c>
       <c r="AB50" s="9">
-        <v>25132.6</v>
+        <v>25132.5</v>
       </c>
       <c r="AC50" s="9">
         <v>14957.4</v>
       </c>
       <c r="AD50" s="9">
-        <v>17801.7</v>
+        <v>17801.8</v>
       </c>
       <c r="AE50" s="9">
         <v>7334.6</v>
@@ -6115,19 +6115,19 @@
         <v>23786</v>
       </c>
       <c r="Q51" s="9">
-        <v>40900.9</v>
+        <v>40901.599999999999</v>
       </c>
       <c r="R51" s="9">
-        <v>25783.3</v>
+        <v>25784</v>
       </c>
       <c r="S51" s="9">
         <v>15117.6</v>
       </c>
       <c r="T51" s="9">
-        <v>18290.7</v>
+        <v>18290.8</v>
       </c>
       <c r="U51" s="9">
-        <v>7587.3</v>
+        <v>7587.4</v>
       </c>
       <c r="W51" s="8">
         <v>71862</v>
@@ -6139,16 +6139,16 @@
         <v>22684</v>
       </c>
       <c r="AA51" s="9">
-        <v>40726.9</v>
+        <v>40727.199999999997</v>
       </c>
       <c r="AB51" s="9">
-        <v>25524</v>
+        <v>25524.400000000001</v>
       </c>
       <c r="AC51" s="9">
         <v>15202.9</v>
       </c>
       <c r="AD51" s="9">
-        <v>18351.099999999999</v>
+        <v>18351.2</v>
       </c>
       <c r="AE51" s="9">
         <v>7236.7</v>
@@ -6183,7 +6183,7 @@
         <v>7644.7</v>
       </c>
       <c r="M52" s="8">
-        <v>73161</v>
+        <v>73160</v>
       </c>
       <c r="O52" s="8">
         <v>51450</v>
@@ -6192,19 +6192,19 @@
         <v>21849</v>
       </c>
       <c r="Q52" s="9">
-        <v>41694.9</v>
+        <v>41695.800000000003</v>
       </c>
       <c r="R52" s="9">
-        <v>26016.5</v>
+        <v>26017.3</v>
       </c>
       <c r="S52" s="9">
-        <v>15678.4</v>
+        <v>15678.5</v>
       </c>
       <c r="T52" s="9">
-        <v>19028.400000000001</v>
+        <v>19028.3</v>
       </c>
       <c r="U52" s="9">
-        <v>7025.4</v>
+        <v>7025.5</v>
       </c>
       <c r="W52" s="8">
         <v>73795</v>
@@ -6266,22 +6266,22 @@
         <v>54187</v>
       </c>
       <c r="P53" s="8">
-        <v>22062</v>
+        <v>22061</v>
       </c>
       <c r="Q53" s="9">
-        <v>44490.8</v>
+        <v>44489.4</v>
       </c>
       <c r="R53" s="9">
-        <v>27224.7</v>
+        <v>27223.4</v>
       </c>
       <c r="S53" s="9">
         <v>17266</v>
       </c>
       <c r="T53" s="9">
-        <v>20113.7</v>
+        <v>20113.599999999999</v>
       </c>
       <c r="U53" s="9">
-        <v>7174.5</v>
+        <v>7174.3</v>
       </c>
       <c r="W53" s="8">
         <v>77180</v>
@@ -6293,16 +6293,16 @@
         <v>22558</v>
       </c>
       <c r="AA53" s="9">
-        <v>44485</v>
+        <v>44484.5</v>
       </c>
       <c r="AB53" s="9">
-        <v>27329.4</v>
+        <v>27328.9</v>
       </c>
       <c r="AC53" s="9">
-        <v>17155.7</v>
+        <v>17155.599999999999</v>
       </c>
       <c r="AD53" s="9">
-        <v>20085.2</v>
+        <v>20085.099999999999</v>
       </c>
       <c r="AE53" s="9">
         <v>7273.2</v>
@@ -6337,28 +6337,28 @@
         <v>7639.3</v>
       </c>
       <c r="M54" s="8">
-        <v>82737</v>
+        <v>82738</v>
       </c>
       <c r="O54" s="8">
-        <v>58532</v>
+        <v>58533</v>
       </c>
       <c r="P54" s="8">
-        <v>23597</v>
+        <v>23596</v>
       </c>
       <c r="Q54" s="9">
-        <v>47780</v>
+        <v>47779</v>
       </c>
       <c r="R54" s="9">
-        <v>28933.8</v>
+        <v>28932.9</v>
       </c>
       <c r="S54" s="9">
-        <v>18846.2</v>
+        <v>18846.099999999999</v>
       </c>
       <c r="T54" s="9">
         <v>21329</v>
       </c>
       <c r="U54" s="9">
-        <v>7556.3</v>
+        <v>7556.4</v>
       </c>
       <c r="W54" s="8">
         <v>80756</v>
@@ -6370,10 +6370,10 @@
         <v>23008</v>
       </c>
       <c r="AA54" s="9">
-        <v>47128.2</v>
+        <v>47128.1</v>
       </c>
       <c r="AB54" s="9">
-        <v>28417.200000000001</v>
+        <v>28417.1</v>
       </c>
       <c r="AC54" s="9">
         <v>18711</v>
@@ -6420,22 +6420,22 @@
         <v>58961</v>
       </c>
       <c r="P55" s="8">
-        <v>23478</v>
+        <v>23479</v>
       </c>
       <c r="Q55" s="9">
-        <v>48900.2</v>
+        <v>48901.599999999999</v>
       </c>
       <c r="R55" s="9">
-        <v>28963.200000000001</v>
+        <v>28964.6</v>
       </c>
       <c r="S55" s="9">
-        <v>19937</v>
+        <v>19936.900000000001</v>
       </c>
       <c r="T55" s="9">
-        <v>21544.7</v>
+        <v>21544.9</v>
       </c>
       <c r="U55" s="9">
-        <v>7569.6</v>
+        <v>7569.7</v>
       </c>
       <c r="W55" s="8">
         <v>83189</v>
@@ -6447,19 +6447,19 @@
         <v>23402</v>
       </c>
       <c r="AA55" s="9">
-        <v>49788</v>
+        <v>49788.5</v>
       </c>
       <c r="AB55" s="9">
-        <v>29483.599999999999</v>
+        <v>29484.1</v>
       </c>
       <c r="AC55" s="9">
         <v>20304.400000000001</v>
       </c>
       <c r="AD55" s="9">
-        <v>21992.799999999999</v>
+        <v>21992.9</v>
       </c>
       <c r="AE55" s="9">
-        <v>7578.7</v>
+        <v>7578.8</v>
       </c>
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.2">
@@ -6500,19 +6500,19 @@
         <v>22962</v>
       </c>
       <c r="Q56" s="9">
-        <v>52530.6</v>
+        <v>52532.1</v>
       </c>
       <c r="R56" s="9">
-        <v>30521.9</v>
+        <v>30523.1</v>
       </c>
       <c r="S56" s="9">
-        <v>22008.799999999999</v>
+        <v>22009</v>
       </c>
       <c r="T56" s="9">
         <v>23080.2</v>
       </c>
       <c r="U56" s="9">
-        <v>7564.9</v>
+        <v>7565</v>
       </c>
       <c r="W56" s="8">
         <v>84046</v>
@@ -6524,13 +6524,13 @@
         <v>23144</v>
       </c>
       <c r="AA56" s="9">
-        <v>51882.9</v>
+        <v>51883</v>
       </c>
       <c r="AB56" s="9">
         <v>30361.7</v>
       </c>
       <c r="AC56" s="9">
-        <v>21521.200000000001</v>
+        <v>21521.3</v>
       </c>
       <c r="AD56" s="9">
         <v>22777.9</v>
@@ -6568,7 +6568,7 @@
         <v>7018.6</v>
       </c>
       <c r="M57" s="8">
-        <v>83807</v>
+        <v>83806</v>
       </c>
       <c r="O57" s="8">
         <v>60845</v>
@@ -6577,19 +6577,19 @@
         <v>22786</v>
       </c>
       <c r="Q57" s="9">
-        <v>53574.7</v>
+        <v>53572.1</v>
       </c>
       <c r="R57" s="9">
-        <v>31150.7</v>
+        <v>31148.1</v>
       </c>
       <c r="S57" s="9">
         <v>22424</v>
       </c>
       <c r="T57" s="9">
-        <v>23393</v>
+        <v>23392.7</v>
       </c>
       <c r="U57" s="9">
-        <v>7712.8</v>
+        <v>7712.4</v>
       </c>
       <c r="W57" s="8">
         <v>84126</v>
@@ -6601,19 +6601,19 @@
         <v>22713</v>
       </c>
       <c r="AA57" s="9">
-        <v>53310</v>
+        <v>53309.2</v>
       </c>
       <c r="AB57" s="9">
-        <v>30941.3</v>
+        <v>30940.6</v>
       </c>
       <c r="AC57" s="9">
-        <v>22368.7</v>
+        <v>22368.6</v>
       </c>
       <c r="AD57" s="9">
-        <v>23309.8</v>
+        <v>23309.7</v>
       </c>
       <c r="AE57" s="9">
-        <v>7649.7</v>
+        <v>7649.6</v>
       </c>
     </row>
     <row r="58" spans="1:31" x14ac:dyDescent="0.2">
@@ -6645,28 +6645,28 @@
         <v>7708</v>
       </c>
       <c r="M58" s="8">
-        <v>84403</v>
+        <v>84404</v>
       </c>
       <c r="O58" s="8">
-        <v>61381</v>
+        <v>61382</v>
       </c>
       <c r="P58" s="8">
         <v>22313</v>
       </c>
       <c r="Q58" s="9">
-        <v>53808.6</v>
+        <v>53807.4</v>
       </c>
       <c r="R58" s="9">
-        <v>31146.400000000001</v>
+        <v>31145.4</v>
       </c>
       <c r="S58" s="9">
-        <v>22662.2</v>
+        <v>22661.9</v>
       </c>
       <c r="T58" s="9">
-        <v>23449.1</v>
+        <v>23449.200000000001</v>
       </c>
       <c r="U58" s="9">
-        <v>7616.7</v>
+        <v>7616.9</v>
       </c>
       <c r="W58" s="8">
         <v>83912</v>
@@ -6678,13 +6678,13 @@
         <v>22488</v>
       </c>
       <c r="AA58" s="9">
-        <v>54276.6</v>
+        <v>54276.5</v>
       </c>
       <c r="AB58" s="9">
         <v>31125.1</v>
       </c>
       <c r="AC58" s="9">
-        <v>23151.5</v>
+        <v>23151.4</v>
       </c>
       <c r="AD58" s="9">
         <v>23553.599999999999</v>
@@ -6731,16 +6731,16 @@
         <v>22459</v>
       </c>
       <c r="Q59" s="9">
-        <v>55192</v>
+        <v>55194.8</v>
       </c>
       <c r="R59" s="9">
-        <v>30932.2</v>
+        <v>30934.9</v>
       </c>
       <c r="S59" s="9">
-        <v>24259.8</v>
+        <v>24259.9</v>
       </c>
       <c r="T59" s="9">
-        <v>23696.7</v>
+        <v>23697</v>
       </c>
       <c r="U59" s="9">
         <v>7561.6</v>
@@ -6755,10 +6755,10 @@
         <v>22339</v>
       </c>
       <c r="AA59" s="9">
-        <v>55300.7</v>
+        <v>55301.4</v>
       </c>
       <c r="AB59" s="9">
-        <v>31158.1</v>
+        <v>31158.799999999999</v>
       </c>
       <c r="AC59" s="9">
         <v>24142.6</v>
@@ -6799,46 +6799,46 @@
         <v>7897.2</v>
       </c>
       <c r="M60" s="8">
-        <v>82999</v>
+        <v>82998</v>
       </c>
       <c r="O60" s="8">
         <v>61300</v>
       </c>
       <c r="P60" s="8">
-        <v>22096</v>
+        <v>22095</v>
       </c>
       <c r="Q60" s="9">
-        <v>56767.5</v>
+        <v>56768.7</v>
       </c>
       <c r="R60" s="9">
-        <v>31359.9</v>
+        <v>31361</v>
       </c>
       <c r="S60" s="9">
-        <v>25407.599999999999</v>
+        <v>25407.8</v>
       </c>
       <c r="T60" s="9">
-        <v>24045.9</v>
+        <v>24045.8</v>
       </c>
       <c r="U60" s="9">
-        <v>7429.6</v>
+        <v>7429.7</v>
       </c>
       <c r="W60" s="8">
-        <v>83463</v>
+        <v>83462</v>
       </c>
       <c r="Y60" s="8">
-        <v>61669</v>
+        <v>61668</v>
       </c>
       <c r="Z60" s="8">
         <v>22067</v>
       </c>
       <c r="AA60" s="9">
-        <v>56651.5</v>
+        <v>56651.199999999997</v>
       </c>
       <c r="AB60" s="9">
-        <v>31239.4</v>
+        <v>31239</v>
       </c>
       <c r="AC60" s="9">
-        <v>25412.1</v>
+        <v>25412.2</v>
       </c>
       <c r="AD60" s="9">
         <v>23886.2</v>
@@ -6879,25 +6879,25 @@
         <v>84842</v>
       </c>
       <c r="O61" s="8">
-        <v>63150</v>
+        <v>63149</v>
       </c>
       <c r="P61" s="8">
         <v>21695</v>
       </c>
       <c r="Q61" s="9">
-        <v>58178</v>
+        <v>58173.599999999999</v>
       </c>
       <c r="R61" s="9">
-        <v>32231</v>
+        <v>32226.5</v>
       </c>
       <c r="S61" s="9">
-        <v>25947</v>
+        <v>25947.1</v>
       </c>
       <c r="T61" s="9">
-        <v>24760.2</v>
+        <v>24759.8</v>
       </c>
       <c r="U61" s="9">
-        <v>7403.8</v>
+        <v>7403.4</v>
       </c>
       <c r="W61" s="8">
         <v>83823</v>
@@ -6909,16 +6909,16 @@
         <v>21671</v>
       </c>
       <c r="AA61" s="9">
-        <v>58126.1</v>
+        <v>58125</v>
       </c>
       <c r="AB61" s="9">
-        <v>31944.7</v>
+        <v>31943.599999999999</v>
       </c>
       <c r="AC61" s="9">
         <v>26181.4</v>
       </c>
       <c r="AD61" s="9">
-        <v>24548.799999999999</v>
+        <v>24548.7</v>
       </c>
       <c r="AE61" s="9">
         <v>7406.9</v>
@@ -6953,28 +6953,28 @@
         <v>7440.8</v>
       </c>
       <c r="M62" s="8">
-        <v>83348</v>
+        <v>83349</v>
       </c>
       <c r="O62" s="8">
-        <v>61575</v>
+        <v>61576</v>
       </c>
       <c r="P62" s="8">
         <v>21008</v>
       </c>
       <c r="Q62" s="9">
-        <v>58332.1</v>
+        <v>58331.1</v>
       </c>
       <c r="R62" s="9">
-        <v>32223</v>
+        <v>32222.400000000001</v>
       </c>
       <c r="S62" s="9">
-        <v>26109.1</v>
+        <v>26108.7</v>
       </c>
       <c r="T62" s="9">
-        <v>24740.9</v>
+        <v>24741.200000000001</v>
       </c>
       <c r="U62" s="9">
-        <v>7353</v>
+        <v>7353.3</v>
       </c>
       <c r="W62" s="8">
         <v>84893</v>
@@ -6986,16 +6986,16 @@
         <v>21119</v>
       </c>
       <c r="AA62" s="9">
-        <v>58928.800000000003</v>
+        <v>58929.599999999999</v>
       </c>
       <c r="AB62" s="9">
-        <v>33624</v>
+        <v>33624.9</v>
       </c>
       <c r="AC62" s="9">
-        <v>25304.799999999999</v>
+        <v>25304.7</v>
       </c>
       <c r="AD62" s="9">
-        <v>26239.599999999999</v>
+        <v>26239.7</v>
       </c>
       <c r="AE62" s="9">
         <v>7377.6</v>
@@ -7033,25 +7033,25 @@
         <v>86824</v>
       </c>
       <c r="O63" s="8">
-        <v>66524</v>
+        <v>66525</v>
       </c>
       <c r="P63" s="8">
-        <v>20838</v>
+        <v>20839</v>
       </c>
       <c r="Q63" s="9">
-        <v>59715.199999999997</v>
+        <v>59722.1</v>
       </c>
       <c r="R63" s="9">
-        <v>36486.5</v>
+        <v>36493.300000000003</v>
       </c>
       <c r="S63" s="9">
-        <v>23228.6</v>
+        <v>23228.799999999999</v>
       </c>
       <c r="T63" s="9">
-        <v>29341</v>
+        <v>29341.3</v>
       </c>
       <c r="U63" s="9">
-        <v>7393.6</v>
+        <v>7393.5</v>
       </c>
       <c r="W63" s="8">
         <v>85541</v>
@@ -7063,13 +7063,13 @@
         <v>20550</v>
       </c>
       <c r="AA63" s="9">
-        <v>58038.400000000001</v>
+        <v>58039.9</v>
       </c>
       <c r="AB63" s="9">
-        <v>35289.199999999997</v>
+        <v>35290.800000000003</v>
       </c>
       <c r="AC63" s="9">
-        <v>22749.200000000001</v>
+        <v>22749.1</v>
       </c>
       <c r="AD63" s="9">
         <v>28029.1</v>
@@ -7107,25 +7107,25 @@
         <v>7690.1</v>
       </c>
       <c r="M64" s="8">
-        <v>86394</v>
+        <v>86393</v>
       </c>
       <c r="O64" s="8">
-        <v>66498</v>
+        <v>66497</v>
       </c>
       <c r="P64" s="8">
         <v>19968</v>
       </c>
       <c r="Q64" s="9">
-        <v>55699.5</v>
+        <v>55699.199999999997</v>
       </c>
       <c r="R64" s="9">
-        <v>36750.800000000003</v>
+        <v>36750.5</v>
       </c>
       <c r="S64" s="9">
-        <v>18948.599999999999</v>
+        <v>18948.7</v>
       </c>
       <c r="T64" s="9">
-        <v>29520.400000000001</v>
+        <v>29520.1</v>
       </c>
       <c r="U64" s="9">
         <v>7160.1</v>
@@ -7134,25 +7134,25 @@
         <v>86279</v>
       </c>
       <c r="Y64" s="8">
-        <v>65916</v>
+        <v>65915</v>
       </c>
       <c r="Z64" s="8">
         <v>20355</v>
       </c>
       <c r="AA64" s="9">
-        <v>56152.3</v>
+        <v>56150.400000000001</v>
       </c>
       <c r="AB64" s="9">
-        <v>36148.9</v>
+        <v>36147</v>
       </c>
       <c r="AC64" s="9">
-        <v>20003.400000000001</v>
+        <v>20003.5</v>
       </c>
       <c r="AD64" s="9">
-        <v>28894.6</v>
+        <v>28894.5</v>
       </c>
       <c r="AE64" s="9">
-        <v>7216.6</v>
+        <v>7216.5</v>
       </c>
     </row>
     <row r="65" spans="1:31" x14ac:dyDescent="0.2">
@@ -7187,40 +7187,40 @@
         <v>84630</v>
       </c>
       <c r="O65" s="8">
-        <v>64122</v>
+        <v>64120</v>
       </c>
       <c r="P65" s="8">
-        <v>20297</v>
+        <v>20296</v>
       </c>
       <c r="Q65" s="9">
-        <v>53261.4</v>
+        <v>53251.8</v>
       </c>
       <c r="R65" s="9">
-        <v>34685.300000000003</v>
+        <v>34675.699999999997</v>
       </c>
       <c r="S65" s="9">
         <v>18576.099999999999</v>
       </c>
       <c r="T65" s="9">
-        <v>27452.2</v>
+        <v>27452</v>
       </c>
       <c r="U65" s="9">
-        <v>7065.6</v>
+        <v>7065.1</v>
       </c>
       <c r="W65" s="8">
-        <v>86479</v>
+        <v>86480</v>
       </c>
       <c r="Y65" s="8">
-        <v>65796</v>
+        <v>65795</v>
       </c>
       <c r="Z65" s="8">
         <v>20486</v>
       </c>
       <c r="AA65" s="9">
-        <v>54724.4</v>
+        <v>54722.6</v>
       </c>
       <c r="AB65" s="9">
-        <v>35847.5</v>
+        <v>35845.699999999997</v>
       </c>
       <c r="AC65" s="9">
         <v>18876.900000000001</v>
@@ -7229,7 +7229,7 @@
         <v>28564</v>
       </c>
       <c r="AE65" s="9">
-        <v>7182.2</v>
+        <v>7182.1</v>
       </c>
     </row>
     <row r="66" spans="1:31" x14ac:dyDescent="0.2">
@@ -7261,46 +7261,46 @@
         <v>7443.1</v>
       </c>
       <c r="M66" s="8">
-        <v>88784</v>
+        <v>88785</v>
       </c>
       <c r="O66" s="8">
-        <v>66664</v>
+        <v>66666</v>
       </c>
       <c r="P66" s="8">
-        <v>21300</v>
+        <v>21299</v>
       </c>
       <c r="Q66" s="9">
         <v>56223.5</v>
       </c>
       <c r="R66" s="9">
-        <v>35943.300000000003</v>
+        <v>35943.4</v>
       </c>
       <c r="S66" s="9">
-        <v>20280.2</v>
+        <v>20280.099999999999</v>
       </c>
       <c r="T66" s="9">
-        <v>28396.3</v>
+        <v>28397</v>
       </c>
       <c r="U66" s="9">
-        <v>7361.1</v>
+        <v>7361.8</v>
       </c>
       <c r="W66" s="8">
         <v>85399</v>
       </c>
       <c r="Y66" s="8">
-        <v>64657</v>
+        <v>64658</v>
       </c>
       <c r="Z66" s="8">
         <v>20530</v>
       </c>
       <c r="AA66" s="9">
-        <v>55062.5</v>
+        <v>55064.9</v>
       </c>
       <c r="AB66" s="9">
-        <v>35066.9</v>
+        <v>35069.4</v>
       </c>
       <c r="AC66" s="9">
-        <v>19995.599999999999</v>
+        <v>19995.5</v>
       </c>
       <c r="AD66" s="9">
         <v>27857.599999999999</v>
@@ -7338,52 +7338,52 @@
         <v>7057.3</v>
       </c>
       <c r="M67" s="8">
-        <v>82569</v>
+        <v>82568</v>
       </c>
       <c r="O67" s="8">
-        <v>63252</v>
+        <v>63256</v>
       </c>
       <c r="P67" s="8">
-        <v>20024</v>
+        <v>20025</v>
       </c>
       <c r="Q67" s="9">
-        <v>56557.599999999999</v>
+        <v>56576.4</v>
       </c>
       <c r="R67" s="9">
-        <v>34534</v>
+        <v>34552.800000000003</v>
       </c>
       <c r="S67" s="9">
-        <v>22023.599999999999</v>
+        <v>22023.5</v>
       </c>
       <c r="T67" s="9">
-        <v>27793.5</v>
+        <v>27793.4</v>
       </c>
       <c r="U67" s="9">
-        <v>7043.9</v>
+        <v>7043.5</v>
       </c>
       <c r="W67" s="8">
-        <v>84716</v>
+        <v>84715</v>
       </c>
       <c r="Y67" s="8">
-        <v>64472</v>
+        <v>64473</v>
       </c>
       <c r="Z67" s="8">
         <v>20371</v>
       </c>
       <c r="AA67" s="9">
-        <v>57431.7</v>
+        <v>57434.3</v>
       </c>
       <c r="AB67" s="9">
-        <v>35108.1</v>
+        <v>35110.699999999997</v>
       </c>
       <c r="AC67" s="9">
-        <v>22323.599999999999</v>
+        <v>22323.5</v>
       </c>
       <c r="AD67" s="9">
-        <v>28045.8</v>
+        <v>28045.599999999999</v>
       </c>
       <c r="AE67" s="9">
-        <v>7119.5</v>
+        <v>7119.4</v>
       </c>
     </row>
     <row r="68" spans="1:31" x14ac:dyDescent="0.2">
@@ -7415,46 +7415,46 @@
         <v>7623.3</v>
       </c>
       <c r="M68" s="8">
-        <v>84147</v>
+        <v>84146</v>
       </c>
       <c r="O68" s="8">
-        <v>64298</v>
+        <v>64294</v>
       </c>
       <c r="P68" s="8">
         <v>20010</v>
       </c>
       <c r="Q68" s="9">
-        <v>60036.5</v>
+        <v>60024.3</v>
       </c>
       <c r="R68" s="9">
-        <v>35630.199999999997</v>
+        <v>35618</v>
       </c>
       <c r="S68" s="9">
         <v>24406.3</v>
       </c>
       <c r="T68" s="9">
-        <v>28528.7</v>
+        <v>28527.8</v>
       </c>
       <c r="U68" s="9">
-        <v>7050.2</v>
+        <v>7050.1</v>
       </c>
       <c r="W68" s="8">
         <v>85319</v>
       </c>
       <c r="Y68" s="8">
-        <v>65463</v>
+        <v>65461</v>
       </c>
       <c r="Z68" s="8">
         <v>20332</v>
       </c>
       <c r="AA68" s="9">
-        <v>59932</v>
+        <v>59926.5</v>
       </c>
       <c r="AB68" s="9">
-        <v>35840.9</v>
+        <v>35835.300000000003</v>
       </c>
       <c r="AC68" s="9">
-        <v>24091.1</v>
+        <v>24091.200000000001</v>
       </c>
       <c r="AD68" s="9">
         <v>28843.200000000001</v>
@@ -7492,52 +7492,52 @@
         <v>6559.7</v>
       </c>
       <c r="M69" s="8">
-        <v>89498</v>
+        <v>89499</v>
       </c>
       <c r="O69" s="8">
-        <v>68675</v>
+        <v>68673</v>
       </c>
       <c r="P69" s="8">
-        <v>20851</v>
+        <v>20849</v>
       </c>
       <c r="Q69" s="9">
-        <v>62646.1</v>
+        <v>62631.3</v>
       </c>
       <c r="R69" s="9">
-        <v>37477.699999999997</v>
+        <v>37462.9</v>
       </c>
       <c r="S69" s="9">
         <v>25168.400000000001</v>
       </c>
       <c r="T69" s="9">
-        <v>30145.4</v>
+        <v>30146.1</v>
       </c>
       <c r="U69" s="9">
-        <v>7266.6</v>
+        <v>7266.7</v>
       </c>
       <c r="W69" s="8">
         <v>87974</v>
       </c>
       <c r="Y69" s="8">
-        <v>67174</v>
+        <v>67173</v>
       </c>
       <c r="Z69" s="8">
-        <v>20730</v>
+        <v>20729</v>
       </c>
       <c r="AA69" s="9">
-        <v>61552.4</v>
+        <v>61548.800000000003</v>
       </c>
       <c r="AB69" s="9">
-        <v>37092.300000000003</v>
+        <v>37088.6</v>
       </c>
       <c r="AC69" s="9">
-        <v>24460.1</v>
+        <v>24460.2</v>
       </c>
       <c r="AD69" s="9">
-        <v>29792</v>
+        <v>29792.400000000001</v>
       </c>
       <c r="AE69" s="9">
-        <v>7238.2</v>
+        <v>7238.4</v>
       </c>
     </row>
     <row r="70" spans="1:31" x14ac:dyDescent="0.2">
@@ -7569,43 +7569,43 @@
         <v>7566.5</v>
       </c>
       <c r="M70" s="8">
-        <v>90155</v>
+        <v>90157</v>
       </c>
       <c r="O70" s="8">
         <v>67813</v>
       </c>
       <c r="P70" s="8">
-        <v>21579</v>
+        <v>21578</v>
       </c>
       <c r="Q70" s="9">
-        <v>61051</v>
+        <v>61054.7</v>
       </c>
       <c r="R70" s="9">
-        <v>38166.400000000001</v>
+        <v>38169.599999999999</v>
       </c>
       <c r="S70" s="9">
-        <v>22884.7</v>
+        <v>22885.1</v>
       </c>
       <c r="T70" s="9">
-        <v>30472.2</v>
+        <v>30473.599999999999</v>
       </c>
       <c r="U70" s="9">
-        <v>7502.8</v>
+        <v>7503.5</v>
       </c>
       <c r="W70" s="8">
         <v>91094</v>
       </c>
       <c r="Y70" s="8">
-        <v>68103</v>
+        <v>68105</v>
       </c>
       <c r="Z70" s="8">
-        <v>21311</v>
+        <v>21312</v>
       </c>
       <c r="AA70" s="9">
-        <v>61933.2</v>
+        <v>61942.1</v>
       </c>
       <c r="AB70" s="9">
-        <v>38459.599999999999</v>
+        <v>38468.5</v>
       </c>
       <c r="AC70" s="9">
         <v>23473.599999999999</v>
@@ -7646,52 +7646,52 @@
         <v>9365.5</v>
       </c>
       <c r="M71" s="8">
-        <v>93218</v>
+        <v>93217</v>
       </c>
       <c r="O71" s="8">
-        <v>67186</v>
+        <v>67194</v>
       </c>
       <c r="P71" s="8">
-        <v>26341</v>
+        <v>26346</v>
       </c>
       <c r="Q71" s="9">
-        <v>61446</v>
+        <v>61487.4</v>
       </c>
       <c r="R71" s="9">
-        <v>39594.5</v>
+        <v>39636.6</v>
       </c>
       <c r="S71" s="9">
-        <v>21851.5</v>
+        <v>21850.9</v>
       </c>
       <c r="T71" s="9">
-        <v>30470.3</v>
+        <v>30468.6</v>
       </c>
       <c r="U71" s="9">
-        <v>9233.2000000000007</v>
+        <v>9232.7000000000007</v>
       </c>
       <c r="W71" s="8">
-        <v>91555</v>
+        <v>91554</v>
       </c>
       <c r="Y71" s="8">
-        <v>66451</v>
+        <v>66453</v>
       </c>
       <c r="Z71" s="8">
-        <v>26580</v>
+        <v>26581</v>
       </c>
       <c r="AA71" s="9">
-        <v>60937.9</v>
+        <v>60944.3</v>
       </c>
       <c r="AB71" s="9">
-        <v>39084.300000000003</v>
+        <v>39091</v>
       </c>
       <c r="AC71" s="9">
-        <v>21853.5</v>
+        <v>21853.3</v>
       </c>
       <c r="AD71" s="9">
-        <v>30259</v>
+        <v>30258.400000000001</v>
       </c>
       <c r="AE71" s="9">
-        <v>9282</v>
+        <v>9281.7999999999993</v>
       </c>
     </row>
     <row r="72" spans="1:31" x14ac:dyDescent="0.2">
@@ -7723,52 +7723,52 @@
         <v>10273.700000000001</v>
       </c>
       <c r="M72" s="8">
-        <v>89488</v>
+        <v>89485</v>
       </c>
       <c r="O72" s="8">
-        <v>63127</v>
+        <v>63126</v>
       </c>
       <c r="P72" s="8">
-        <v>26615</v>
+        <v>26614</v>
       </c>
       <c r="Q72" s="9">
-        <v>59375</v>
+        <v>59350.7</v>
       </c>
       <c r="R72" s="9">
-        <v>38951.4</v>
+        <v>38927.4</v>
       </c>
       <c r="S72" s="9">
-        <v>20423.599999999999</v>
+        <v>20423.3</v>
       </c>
       <c r="T72" s="9">
-        <v>29433.7</v>
+        <v>29432.7</v>
       </c>
       <c r="U72" s="9">
-        <v>9554</v>
+        <v>9552.5</v>
       </c>
       <c r="W72" s="8">
         <v>90127</v>
       </c>
       <c r="Y72" s="8">
-        <v>63594</v>
+        <v>63593</v>
       </c>
       <c r="Z72" s="8">
         <v>26553</v>
       </c>
       <c r="AA72" s="9">
-        <v>59584.1</v>
+        <v>59571.4</v>
       </c>
       <c r="AB72" s="9">
-        <v>39234.1</v>
+        <v>39221.4</v>
       </c>
       <c r="AC72" s="9">
-        <v>20349.900000000001</v>
+        <v>20350</v>
       </c>
       <c r="AD72" s="9">
-        <v>29678.400000000001</v>
+        <v>29678.3</v>
       </c>
       <c r="AE72" s="9">
-        <v>9521.4</v>
+        <v>9521.2999999999993</v>
       </c>
     </row>
     <row r="73" spans="1:31" x14ac:dyDescent="0.2">
@@ -7800,52 +7800,52 @@
         <v>8843.1</v>
       </c>
       <c r="M73" s="8">
-        <v>87108</v>
+        <v>87113</v>
       </c>
       <c r="O73" s="8">
-        <v>60404</v>
+        <v>60395</v>
       </c>
       <c r="P73" s="8">
-        <v>26466</v>
+        <v>26464</v>
       </c>
       <c r="Q73" s="9">
-        <v>57785.8</v>
+        <v>57738.6</v>
       </c>
       <c r="R73" s="9">
-        <v>38753.199999999997</v>
+        <v>38705.4</v>
       </c>
       <c r="S73" s="9">
-        <v>19032.5</v>
+        <v>19033.2</v>
       </c>
       <c r="T73" s="9">
-        <v>28895.1</v>
+        <v>28896.9</v>
       </c>
       <c r="U73" s="9">
-        <v>9666.6</v>
+        <v>9668.7999999999993</v>
       </c>
       <c r="W73" s="8">
-        <v>88043</v>
+        <v>88044</v>
       </c>
       <c r="Y73" s="8">
-        <v>61190</v>
+        <v>61187</v>
       </c>
       <c r="Z73" s="8">
-        <v>26445</v>
+        <v>26444</v>
       </c>
       <c r="AA73" s="9">
-        <v>58177.5</v>
+        <v>58167.1</v>
       </c>
       <c r="AB73" s="9">
-        <v>39065.1</v>
+        <v>39054.400000000001</v>
       </c>
       <c r="AC73" s="9">
-        <v>19112.400000000001</v>
+        <v>19112.8</v>
       </c>
       <c r="AD73" s="9">
-        <v>29165.7</v>
+        <v>29166.9</v>
       </c>
       <c r="AE73" s="9">
-        <v>9731.4</v>
+        <v>9731.9</v>
       </c>
     </row>
     <row r="74" spans="1:31" x14ac:dyDescent="0.2">
@@ -7877,28 +7877,28 @@
         <v>9938.2000000000007</v>
       </c>
       <c r="M74" s="8">
-        <v>86804</v>
+        <v>86806</v>
       </c>
       <c r="O74" s="8">
-        <v>60130</v>
+        <v>60131</v>
       </c>
       <c r="P74" s="8">
-        <v>26065</v>
+        <v>26064</v>
       </c>
       <c r="Q74" s="9">
-        <v>56715.9</v>
+        <v>56744.2</v>
       </c>
       <c r="R74" s="9">
-        <v>38929.800000000003</v>
+        <v>38957.4</v>
       </c>
       <c r="S74" s="9">
-        <v>17786.2</v>
+        <v>17786.8</v>
       </c>
       <c r="T74" s="9">
-        <v>28936</v>
+        <v>28938.6</v>
       </c>
       <c r="U74" s="9">
-        <v>9873.6</v>
+        <v>9873.7000000000007</v>
       </c>
       <c r="W74" s="8">
         <v>85986</v>
@@ -7910,13 +7910,13 @@
         <v>26218</v>
       </c>
       <c r="AA74" s="9">
-        <v>56338.8</v>
+        <v>56355</v>
       </c>
       <c r="AB74" s="9">
-        <v>38423.800000000003</v>
+        <v>38440</v>
       </c>
       <c r="AC74" s="9">
-        <v>17915</v>
+        <v>17914.900000000001</v>
       </c>
       <c r="AD74" s="9">
         <v>28592.5</v>
@@ -7954,52 +7954,52 @@
         <v>9674.7999999999993</v>
       </c>
       <c r="M75" s="8">
-        <v>83329</v>
+        <v>83325</v>
       </c>
       <c r="O75" s="8">
-        <v>57993</v>
+        <v>58000</v>
       </c>
       <c r="P75" s="8">
-        <v>25898</v>
+        <v>25904</v>
       </c>
       <c r="Q75" s="9">
-        <v>53970.2</v>
+        <v>54033.599999999999</v>
       </c>
       <c r="R75" s="9">
-        <v>37029.9</v>
+        <v>37094.400000000001</v>
       </c>
       <c r="S75" s="9">
-        <v>16940.3</v>
+        <v>16939.2</v>
       </c>
       <c r="T75" s="9">
-        <v>27587.4</v>
+        <v>27584.799999999999</v>
       </c>
       <c r="U75" s="9">
-        <v>9673.1</v>
+        <v>9672.6</v>
       </c>
       <c r="W75" s="8">
-        <v>83589</v>
+        <v>83588</v>
       </c>
       <c r="Y75" s="8">
-        <v>58101</v>
+        <v>58104</v>
       </c>
       <c r="Z75" s="8">
-        <v>25563</v>
+        <v>25564</v>
       </c>
       <c r="AA75" s="9">
-        <v>53660.6</v>
+        <v>53674.1</v>
       </c>
       <c r="AB75" s="9">
-        <v>37000.9</v>
+        <v>37014.800000000003</v>
       </c>
       <c r="AC75" s="9">
-        <v>16659.7</v>
+        <v>16659.3</v>
       </c>
       <c r="AD75" s="9">
-        <v>27484.7</v>
+        <v>27483.4</v>
       </c>
       <c r="AE75" s="9">
-        <v>9570.2999999999993</v>
+        <v>9569.7999999999993</v>
       </c>
     </row>
     <row r="76" spans="1:31" x14ac:dyDescent="0.2">
@@ -8031,49 +8031,49 @@
         <v>9949.7000000000007</v>
       </c>
       <c r="M76" s="8">
-        <v>80865</v>
+        <v>80859</v>
       </c>
       <c r="O76" s="8">
-        <v>56230</v>
+        <v>56233</v>
       </c>
       <c r="P76" s="8">
-        <v>24744</v>
+        <v>24742</v>
       </c>
       <c r="Q76" s="9">
-        <v>50293.3</v>
+        <v>50259.8</v>
       </c>
       <c r="R76" s="9">
-        <v>35022.800000000003</v>
+        <v>34990.5</v>
       </c>
       <c r="S76" s="9">
-        <v>15270.5</v>
+        <v>15269.4</v>
       </c>
       <c r="T76" s="9">
-        <v>25876.6</v>
+        <v>25870.7</v>
       </c>
       <c r="U76" s="9">
-        <v>9207.7999999999993</v>
+        <v>9205.2000000000007</v>
       </c>
       <c r="W76" s="8">
         <v>79687</v>
       </c>
       <c r="Y76" s="8">
-        <v>55316</v>
+        <v>55317</v>
       </c>
       <c r="Z76" s="8">
         <v>24562</v>
       </c>
       <c r="AA76" s="9">
-        <v>49850.8</v>
+        <v>49831.3</v>
       </c>
       <c r="AB76" s="9">
-        <v>34730.9</v>
+        <v>34711.300000000003</v>
       </c>
       <c r="AC76" s="9">
-        <v>15119.9</v>
+        <v>15120</v>
       </c>
       <c r="AD76" s="9">
-        <v>25659.599999999999</v>
+        <v>25659.7</v>
       </c>
       <c r="AE76" s="9">
         <v>9122.9</v>
@@ -8108,52 +8108,52 @@
         <v>8014.2</v>
       </c>
       <c r="M77" s="8">
-        <v>75200</v>
+        <v>75211</v>
       </c>
       <c r="O77" s="8">
-        <v>51698</v>
+        <v>51685</v>
       </c>
       <c r="P77" s="8">
-        <v>23587</v>
+        <v>23586</v>
       </c>
       <c r="Q77" s="9">
-        <v>46263.1</v>
+        <v>46168.5</v>
       </c>
       <c r="R77" s="9">
-        <v>32610.799999999999</v>
+        <v>32513.7</v>
       </c>
       <c r="S77" s="9">
-        <v>13652.3</v>
+        <v>13654.8</v>
       </c>
       <c r="T77" s="9">
-        <v>23740.3</v>
+        <v>23750.400000000001</v>
       </c>
       <c r="U77" s="9">
-        <v>8736.2999999999993</v>
+        <v>8740.7000000000007</v>
       </c>
       <c r="W77" s="8">
-        <v>75956</v>
+        <v>75959</v>
       </c>
       <c r="Y77" s="8">
-        <v>52000</v>
+        <v>51997</v>
       </c>
       <c r="Z77" s="8">
         <v>24006</v>
       </c>
       <c r="AA77" s="9">
-        <v>46741</v>
+        <v>46723.8</v>
       </c>
       <c r="AB77" s="9">
-        <v>32917.199999999997</v>
+        <v>32899.1</v>
       </c>
       <c r="AC77" s="9">
-        <v>13823.9</v>
+        <v>13824.7</v>
       </c>
       <c r="AD77" s="9">
-        <v>23946.9</v>
+        <v>23949.7</v>
       </c>
       <c r="AE77" s="9">
-        <v>8966.9</v>
+        <v>8967.9</v>
       </c>
     </row>
     <row r="78" spans="1:31" x14ac:dyDescent="0.2">
@@ -8185,52 +8185,52 @@
         <v>9328.4</v>
       </c>
       <c r="M78" s="8">
-        <v>73445</v>
+        <v>73447</v>
       </c>
       <c r="O78" s="8">
-        <v>49000</v>
+        <v>49002</v>
       </c>
       <c r="P78" s="8">
-        <v>24217</v>
+        <v>24216</v>
       </c>
       <c r="Q78" s="9">
-        <v>45289.7</v>
+        <v>45360.800000000003</v>
       </c>
       <c r="R78" s="9">
-        <v>32370.9</v>
+        <v>32441.5</v>
       </c>
       <c r="S78" s="9">
-        <v>12918.8</v>
+        <v>12919.4</v>
       </c>
       <c r="T78" s="9">
-        <v>23138.6</v>
+        <v>23139</v>
       </c>
       <c r="U78" s="9">
-        <v>9276</v>
+        <v>9275.2000000000007</v>
       </c>
       <c r="W78" s="8">
-        <v>74947</v>
+        <v>74946</v>
       </c>
       <c r="Y78" s="8">
-        <v>50231</v>
+        <v>50229</v>
       </c>
       <c r="Z78" s="8">
         <v>24726</v>
       </c>
       <c r="AA78" s="9">
-        <v>46724.7</v>
+        <v>46755.5</v>
       </c>
       <c r="AB78" s="9">
-        <v>33204.1</v>
+        <v>33235.1</v>
       </c>
       <c r="AC78" s="9">
-        <v>13520.6</v>
+        <v>13520.4</v>
       </c>
       <c r="AD78" s="9">
-        <v>23710</v>
+        <v>23709.5</v>
       </c>
       <c r="AE78" s="9">
-        <v>9545.5</v>
+        <v>9545.1</v>
       </c>
     </row>
     <row r="79" spans="1:31" x14ac:dyDescent="0.2">
@@ -8268,64 +8268,64 @@
         <v>10867.9</v>
       </c>
       <c r="L79" s="8">
-        <v>108315</v>
+        <v>108301</v>
       </c>
       <c r="M79" s="8">
-        <v>77189</v>
+        <v>77179</v>
       </c>
       <c r="N79" s="8">
-        <v>31127</v>
+        <v>31122</v>
       </c>
       <c r="O79" s="8">
-        <v>50437</v>
+        <v>50438</v>
       </c>
       <c r="P79" s="8">
-        <v>26910</v>
+        <v>26914</v>
       </c>
       <c r="Q79" s="9">
-        <v>49987</v>
+        <v>50073.9</v>
       </c>
       <c r="R79" s="9">
-        <v>35493</v>
+        <v>35582</v>
       </c>
       <c r="S79" s="9">
-        <v>14494</v>
+        <v>14491.9</v>
       </c>
       <c r="T79" s="9">
-        <v>24746.2</v>
+        <v>24741.7</v>
       </c>
       <c r="U79" s="9">
-        <v>10897.9</v>
+        <v>10896.9</v>
       </c>
       <c r="V79" s="8">
-        <v>107998</v>
+        <v>107980</v>
       </c>
       <c r="W79" s="8">
-        <v>76461</v>
+        <v>76456</v>
       </c>
       <c r="X79" s="8">
-        <v>31537</v>
+        <v>31524</v>
       </c>
       <c r="Y79" s="8">
-        <v>50283</v>
+        <v>50285</v>
       </c>
       <c r="Z79" s="8">
         <v>26655</v>
       </c>
       <c r="AA79" s="9">
-        <v>49612.800000000003</v>
+        <v>49623.9</v>
       </c>
       <c r="AB79" s="9">
-        <v>35469.699999999997</v>
+        <v>35482.1</v>
       </c>
       <c r="AC79" s="9">
-        <v>14143</v>
+        <v>14141.8</v>
       </c>
       <c r="AD79" s="9">
-        <v>24960.2</v>
+        <v>24957.1</v>
       </c>
       <c r="AE79" s="9">
-        <v>10706.1</v>
+        <v>10704.9</v>
       </c>
     </row>
     <row r="80" spans="1:31" x14ac:dyDescent="0.2">
@@ -8363,64 +8363,64 @@
         <v>12620.7</v>
       </c>
       <c r="L80" s="8">
-        <v>111866</v>
+        <v>111837</v>
       </c>
       <c r="M80" s="8">
-        <v>80397</v>
+        <v>80381</v>
       </c>
       <c r="N80" s="8">
-        <v>31470</v>
+        <v>31456</v>
       </c>
       <c r="O80" s="8">
-        <v>52324</v>
+        <v>52330</v>
       </c>
       <c r="P80" s="8">
-        <v>28550</v>
+        <v>28543</v>
       </c>
       <c r="Q80" s="9">
-        <v>54389</v>
+        <v>54329</v>
       </c>
       <c r="R80" s="9">
-        <v>39237.9</v>
+        <v>39181.199999999997</v>
       </c>
       <c r="S80" s="9">
-        <v>15151.1</v>
+        <v>15147.8</v>
       </c>
       <c r="T80" s="9">
-        <v>27553.3</v>
+        <v>27540.7</v>
       </c>
       <c r="U80" s="9">
-        <v>11828.4</v>
+        <v>11822.7</v>
       </c>
       <c r="V80" s="8">
-        <v>109606</v>
+        <v>109604</v>
       </c>
       <c r="W80" s="8">
-        <v>78801</v>
+        <v>78805</v>
       </c>
       <c r="X80" s="8">
-        <v>30805</v>
+        <v>30799</v>
       </c>
       <c r="Y80" s="8">
-        <v>50865</v>
+        <v>50868</v>
       </c>
       <c r="Z80" s="8">
         <v>28243</v>
       </c>
       <c r="AA80" s="9">
-        <v>52944.800000000003</v>
+        <v>52892.1</v>
       </c>
       <c r="AB80" s="9">
-        <v>38123</v>
+        <v>38070</v>
       </c>
       <c r="AC80" s="9">
-        <v>14821.9</v>
+        <v>14822</v>
       </c>
       <c r="AD80" s="9">
-        <v>26476.6</v>
+        <v>26477.4</v>
       </c>
       <c r="AE80" s="9">
-        <v>11683.2</v>
+        <v>11683.5</v>
       </c>
     </row>
     <row r="81" spans="1:31" x14ac:dyDescent="0.2">
@@ -8458,64 +8458,64 @@
         <v>11394</v>
       </c>
       <c r="L81" s="8">
-        <v>109522</v>
+        <v>109558</v>
       </c>
       <c r="M81" s="8">
-        <v>79848</v>
+        <v>79885</v>
       </c>
       <c r="N81" s="8">
-        <v>29674</v>
+        <v>29673</v>
       </c>
       <c r="O81" s="8">
-        <v>50272</v>
+        <v>50269</v>
       </c>
       <c r="P81" s="8">
-        <v>29042</v>
+        <v>29049</v>
       </c>
       <c r="Q81" s="9">
-        <v>54636.6</v>
+        <v>54416.2</v>
       </c>
       <c r="R81" s="9">
-        <v>39856.9</v>
+        <v>39630.300000000003</v>
       </c>
       <c r="S81" s="9">
-        <v>14779.7</v>
+        <v>14785.9</v>
       </c>
       <c r="T81" s="9">
-        <v>27162.1</v>
+        <v>27186</v>
       </c>
       <c r="U81" s="9">
-        <v>12185.4</v>
+        <v>12196</v>
       </c>
       <c r="V81" s="8">
-        <v>110600</v>
+        <v>110614</v>
       </c>
       <c r="W81" s="8">
-        <v>80685</v>
+        <v>80697</v>
       </c>
       <c r="X81" s="8">
-        <v>29915</v>
+        <v>29917</v>
       </c>
       <c r="Y81" s="8">
-        <v>50635</v>
+        <v>50634</v>
       </c>
       <c r="Z81" s="8">
-        <v>28250</v>
+        <v>28253</v>
       </c>
       <c r="AA81" s="9">
-        <v>54554.5</v>
+        <v>54525.7</v>
       </c>
       <c r="AB81" s="9">
-        <v>39747.199999999997</v>
+        <v>39715.800000000003</v>
       </c>
       <c r="AC81" s="9">
-        <v>14807.3</v>
+        <v>14809.9</v>
       </c>
       <c r="AD81" s="9">
-        <v>27176.9</v>
+        <v>27184.2</v>
       </c>
       <c r="AE81" s="9">
-        <v>11871.9</v>
+        <v>11874.8</v>
       </c>
     </row>
     <row r="82" spans="1:31" x14ac:dyDescent="0.2">
@@ -8553,64 +8553,64 @@
         <v>11599.6</v>
       </c>
       <c r="L82" s="8">
-        <v>94892</v>
+        <v>94915</v>
       </c>
       <c r="M82" s="8">
-        <v>70788</v>
+        <v>70796</v>
       </c>
       <c r="N82" s="8">
-        <v>24104</v>
+        <v>24119</v>
       </c>
       <c r="O82" s="8">
-        <v>43637</v>
+        <v>43632</v>
       </c>
       <c r="P82" s="8">
-        <v>26950</v>
+        <v>26953</v>
       </c>
       <c r="Q82" s="9">
-        <v>47160</v>
+        <v>47327.7</v>
       </c>
       <c r="R82" s="9">
-        <v>34993</v>
+        <v>35158.300000000003</v>
       </c>
       <c r="S82" s="9">
-        <v>12167</v>
+        <v>12169.4</v>
       </c>
       <c r="T82" s="9">
-        <v>23598.2</v>
+        <v>23599.8</v>
       </c>
       <c r="U82" s="9">
-        <v>11521.6</v>
+        <v>11520.9</v>
       </c>
       <c r="V82" s="8">
-        <v>112912</v>
+        <v>112909</v>
       </c>
       <c r="W82" s="8">
-        <v>83923</v>
+        <v>83916</v>
       </c>
       <c r="X82" s="8">
-        <v>28989</v>
+        <v>28994</v>
       </c>
       <c r="Y82" s="8">
-        <v>50735</v>
+        <v>50729</v>
       </c>
       <c r="Z82" s="8">
-        <v>27647</v>
+        <v>27645</v>
       </c>
       <c r="AA82" s="9">
-        <v>55553</v>
+        <v>55629.8</v>
       </c>
       <c r="AB82" s="9">
-        <v>41218.800000000003</v>
+        <v>41295.4</v>
       </c>
       <c r="AC82" s="9">
-        <v>14334.3</v>
+        <v>14334.4</v>
       </c>
       <c r="AD82" s="9">
-        <v>27618.5</v>
+        <v>27616.9</v>
       </c>
       <c r="AE82" s="9">
-        <v>11698.6</v>
+        <v>11698.5</v>
       </c>
     </row>
     <row r="83" spans="1:31" x14ac:dyDescent="0.2">
@@ -8648,64 +8648,64 @@
         <v>15068.3</v>
       </c>
       <c r="L83" s="8">
-        <v>119696</v>
+        <v>119652</v>
       </c>
       <c r="M83" s="8">
-        <v>90512</v>
+        <v>90472</v>
       </c>
       <c r="N83" s="8">
-        <v>29184</v>
+        <v>29181</v>
       </c>
       <c r="O83" s="8">
-        <v>53052</v>
+        <v>53051</v>
       </c>
       <c r="P83" s="8">
-        <v>37938</v>
+        <v>37935</v>
       </c>
       <c r="Q83" s="9">
-        <v>58339.8</v>
+        <v>58511.5</v>
       </c>
       <c r="R83" s="9">
-        <v>44064.9</v>
+        <v>44241.3</v>
       </c>
       <c r="S83" s="9">
-        <v>14275</v>
+        <v>14270.3</v>
       </c>
       <c r="T83" s="9">
-        <v>29116.2</v>
+        <v>29104.1</v>
       </c>
       <c r="U83" s="9">
-        <v>15330.3</v>
+        <v>15326.4</v>
       </c>
       <c r="V83" s="8">
-        <v>121928</v>
+        <v>121908</v>
       </c>
       <c r="W83" s="8">
-        <v>92365</v>
+        <v>92347</v>
       </c>
       <c r="X83" s="8">
-        <v>29563</v>
+        <v>29561</v>
       </c>
       <c r="Y83" s="8">
-        <v>54247</v>
+        <v>54246</v>
       </c>
       <c r="Z83" s="8">
-        <v>39325</v>
+        <v>39320</v>
       </c>
       <c r="AA83" s="9">
         <v>59908.800000000003</v>
       </c>
       <c r="AB83" s="9">
-        <v>45265</v>
+        <v>45268.4</v>
       </c>
       <c r="AC83" s="9">
-        <v>14643.8</v>
+        <v>14640.3</v>
       </c>
       <c r="AD83" s="9">
-        <v>29664.6</v>
+        <v>29656.9</v>
       </c>
       <c r="AE83" s="9">
-        <v>16079.4</v>
+        <v>16076</v>
       </c>
     </row>
     <row r="84" spans="1:31" x14ac:dyDescent="0.2">
@@ -8743,64 +8743,64 @@
         <v>19194.900000000001</v>
       </c>
       <c r="L84" s="8">
-        <v>134845</v>
+        <v>134789</v>
       </c>
       <c r="M84" s="8">
-        <v>102937</v>
+        <v>102899</v>
       </c>
       <c r="N84" s="8">
-        <v>31908</v>
+        <v>31891</v>
       </c>
       <c r="O84" s="8">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="P84" s="8">
-        <v>42516</v>
+        <v>42479</v>
       </c>
       <c r="Q84" s="9">
-        <v>67513.7</v>
+        <v>67326.100000000006</v>
       </c>
       <c r="R84" s="9">
-        <v>51446.2</v>
+        <v>51268.1</v>
       </c>
       <c r="S84" s="9">
-        <v>16067.5</v>
+        <v>16058</v>
       </c>
       <c r="T84" s="9">
-        <v>33516.1</v>
+        <v>33488.199999999997</v>
       </c>
       <c r="U84" s="9">
-        <v>17768.099999999999</v>
+        <v>17754.8</v>
       </c>
       <c r="V84" s="8">
-        <v>136951</v>
+        <v>136959</v>
       </c>
       <c r="W84" s="8">
-        <v>104466</v>
+        <v>104480</v>
       </c>
       <c r="X84" s="8">
-        <v>32485</v>
+        <v>32479</v>
       </c>
       <c r="Y84" s="8">
-        <v>61300</v>
+        <v>61308</v>
       </c>
       <c r="Z84" s="8">
-        <v>41630</v>
+        <v>41633</v>
       </c>
       <c r="AA84" s="9">
-        <v>68588.100000000006</v>
+        <v>68456.100000000006</v>
       </c>
       <c r="AB84" s="9">
-        <v>52090.5</v>
+        <v>51956.9</v>
       </c>
       <c r="AC84" s="9">
-        <v>16497.5</v>
+        <v>16499.2</v>
       </c>
       <c r="AD84" s="9">
-        <v>34013.9</v>
+        <v>34018.199999999997</v>
       </c>
       <c r="AE84" s="9">
-        <v>17862.7</v>
+        <v>17863.3</v>
       </c>
     </row>
     <row r="85" spans="1:31" x14ac:dyDescent="0.2">
@@ -8838,64 +8838,64 @@
         <v>18750</v>
       </c>
       <c r="L85" s="8">
-        <v>156394</v>
+        <v>156507</v>
       </c>
       <c r="M85" s="8">
-        <v>118453</v>
+        <v>118570</v>
       </c>
       <c r="N85" s="8">
-        <v>37942</v>
+        <v>37937</v>
       </c>
       <c r="O85" s="8">
-        <v>70602</v>
+        <v>70630</v>
       </c>
       <c r="P85" s="8">
-        <v>48161</v>
+        <v>48235</v>
       </c>
       <c r="Q85" s="9">
-        <v>80895.899999999994</v>
+        <v>80390</v>
       </c>
       <c r="R85" s="9">
-        <v>60754.8</v>
+        <v>60233.3</v>
       </c>
       <c r="S85" s="9">
-        <v>20141.2</v>
+        <v>20156.7</v>
       </c>
       <c r="T85" s="9">
-        <v>39853</v>
+        <v>39914</v>
       </c>
       <c r="U85" s="9">
-        <v>20339.099999999999</v>
+        <v>20364</v>
       </c>
       <c r="V85" s="8">
-        <v>151251</v>
+        <v>151302</v>
       </c>
       <c r="W85" s="8">
-        <v>113697</v>
+        <v>113744</v>
       </c>
       <c r="X85" s="8">
-        <v>37553</v>
+        <v>37558</v>
       </c>
       <c r="Y85" s="8">
-        <v>68309</v>
+        <v>68320</v>
       </c>
       <c r="Z85" s="8">
-        <v>43263</v>
+        <v>43279</v>
       </c>
       <c r="AA85" s="9">
-        <v>78562</v>
+        <v>78508.399999999994</v>
       </c>
       <c r="AB85" s="9">
-        <v>58724.6</v>
+        <v>58661.8</v>
       </c>
       <c r="AC85" s="9">
-        <v>19837.400000000001</v>
+        <v>19846.599999999999</v>
       </c>
       <c r="AD85" s="9">
-        <v>39188.400000000001</v>
+        <v>39210.5</v>
       </c>
       <c r="AE85" s="9">
-        <v>19340.900000000001</v>
+        <v>19349.2</v>
       </c>
     </row>
     <row r="86" spans="1:31" x14ac:dyDescent="0.2">
@@ -8933,64 +8933,64 @@
         <v>19482.400000000001</v>
       </c>
       <c r="L86" s="8">
-        <v>158594</v>
+        <v>158671</v>
       </c>
       <c r="M86" s="8">
-        <v>115345</v>
+        <v>115387</v>
       </c>
       <c r="N86" s="8">
-        <v>43249</v>
+        <v>43284</v>
       </c>
       <c r="O86" s="8">
-        <v>72186</v>
+        <v>72178</v>
       </c>
       <c r="P86" s="8">
-        <v>42805</v>
+        <v>42795</v>
       </c>
       <c r="Q86" s="9">
-        <v>86104.4</v>
+        <v>86688.4</v>
       </c>
       <c r="R86" s="9">
-        <v>62297.5</v>
+        <v>62862.7</v>
       </c>
       <c r="S86" s="9">
-        <v>23806.9</v>
+        <v>23825.7</v>
       </c>
       <c r="T86" s="9">
-        <v>43442.2</v>
+        <v>43455.1</v>
       </c>
       <c r="U86" s="9">
-        <v>19300.599999999999</v>
+        <v>19305.2</v>
       </c>
       <c r="V86" s="8">
-        <v>158899</v>
+        <v>158908</v>
       </c>
       <c r="W86" s="8">
-        <v>115259</v>
+        <v>115257</v>
       </c>
       <c r="X86" s="8">
-        <v>43641</v>
+        <v>43652</v>
       </c>
       <c r="Y86" s="8">
-        <v>71793</v>
+        <v>71786</v>
       </c>
       <c r="Z86" s="8">
         <v>42023</v>
       </c>
       <c r="AA86" s="9">
-        <v>86011.6</v>
+        <v>86170</v>
       </c>
       <c r="AB86" s="9">
-        <v>62181.599999999999</v>
+        <v>62339.8</v>
       </c>
       <c r="AC86" s="9">
-        <v>23829.9</v>
+        <v>23830.2</v>
       </c>
       <c r="AD86" s="9">
-        <v>43028.800000000003</v>
+        <v>43029.8</v>
       </c>
       <c r="AE86" s="9">
-        <v>19267.7</v>
+        <v>19270.900000000001</v>
       </c>
     </row>
     <row r="87" spans="1:31" x14ac:dyDescent="0.2">
@@ -9028,64 +9028,64 @@
         <v>17364.099999999999</v>
       </c>
       <c r="L87" s="8">
-        <v>158273</v>
+        <v>158162</v>
       </c>
       <c r="M87" s="8">
-        <v>108805</v>
+        <v>108694</v>
       </c>
       <c r="N87" s="8">
         <v>49468</v>
       </c>
       <c r="O87" s="8">
-        <v>70673</v>
+        <v>70656</v>
       </c>
       <c r="P87" s="8">
-        <v>37971</v>
+        <v>37960</v>
       </c>
       <c r="Q87" s="9">
-        <v>89720.2</v>
+        <v>89977.8</v>
       </c>
       <c r="R87" s="9">
-        <v>62062.5</v>
+        <v>62346</v>
       </c>
       <c r="S87" s="9">
-        <v>27657.7</v>
+        <v>27631.8</v>
       </c>
       <c r="T87" s="9">
-        <v>44870.7</v>
+        <v>44835.8</v>
       </c>
       <c r="U87" s="9">
-        <v>17483.599999999999</v>
+        <v>17474.599999999999</v>
       </c>
       <c r="V87" s="8">
-        <v>159501</v>
+        <v>159449</v>
       </c>
       <c r="W87" s="8">
-        <v>110387</v>
+        <v>110341</v>
       </c>
       <c r="X87" s="8">
-        <v>49114</v>
+        <v>49108</v>
       </c>
       <c r="Y87" s="8">
-        <v>71352</v>
+        <v>71337</v>
       </c>
       <c r="Z87" s="8">
-        <v>38782</v>
+        <v>38770</v>
       </c>
       <c r="AA87" s="9">
-        <v>90450.1</v>
+        <v>90494.3</v>
       </c>
       <c r="AB87" s="9">
-        <v>62638.8</v>
+        <v>62697.4</v>
       </c>
       <c r="AC87" s="9">
-        <v>27811.3</v>
+        <v>27796.9</v>
       </c>
       <c r="AD87" s="9">
-        <v>44792.7</v>
+        <v>44770.9</v>
       </c>
       <c r="AE87" s="9">
-        <v>17959.400000000001</v>
+        <v>17953</v>
       </c>
     </row>
     <row r="88" spans="1:31" x14ac:dyDescent="0.2">
@@ -9123,64 +9123,64 @@
         <v>17715</v>
       </c>
       <c r="L88" s="8">
-        <v>155726</v>
+        <v>155572</v>
       </c>
       <c r="M88" s="8">
-        <v>103268</v>
+        <v>103156</v>
       </c>
       <c r="N88" s="8">
-        <v>52458</v>
+        <v>52415</v>
       </c>
       <c r="O88" s="8">
-        <v>68480</v>
+        <v>68440</v>
       </c>
       <c r="P88" s="8">
-        <v>35157</v>
+        <v>35099</v>
       </c>
       <c r="Q88" s="9">
-        <v>91422.9</v>
+        <v>90997.4</v>
       </c>
       <c r="R88" s="9">
-        <v>60904.9</v>
+        <v>60512.800000000003</v>
       </c>
       <c r="S88" s="9">
-        <v>30518.1</v>
+        <v>30484.7</v>
       </c>
       <c r="T88" s="9">
-        <v>44182.2</v>
+        <v>44110.5</v>
       </c>
       <c r="U88" s="9">
-        <v>16617.7</v>
+        <v>16595.5</v>
       </c>
       <c r="V88" s="8">
-        <v>156596</v>
+        <v>156583</v>
       </c>
       <c r="W88" s="8">
-        <v>104189</v>
+        <v>104193</v>
       </c>
       <c r="X88" s="8">
-        <v>52407</v>
+        <v>52391</v>
       </c>
       <c r="Y88" s="8">
-        <v>69040</v>
+        <v>69044</v>
       </c>
       <c r="Z88" s="8">
-        <v>35516</v>
+        <v>35515</v>
       </c>
       <c r="AA88" s="9">
-        <v>92569.4</v>
+        <v>92396.4</v>
       </c>
       <c r="AB88" s="9">
-        <v>61763.6</v>
+        <v>61595.4</v>
       </c>
       <c r="AC88" s="9">
-        <v>30805.8</v>
+        <v>30801</v>
       </c>
       <c r="AD88" s="9">
-        <v>45026.400000000001</v>
+        <v>45022.8</v>
       </c>
       <c r="AE88" s="9">
-        <v>16605.400000000001</v>
+        <v>16601.8</v>
       </c>
     </row>
     <row r="89" spans="1:31" x14ac:dyDescent="0.2">
@@ -9218,64 +9218,64 @@
         <v>14664.6</v>
       </c>
       <c r="L89" s="8">
-        <v>153068</v>
+        <v>153305</v>
       </c>
       <c r="M89" s="8">
-        <v>100004</v>
+        <v>100255</v>
       </c>
       <c r="N89" s="8">
-        <v>53064</v>
+        <v>53050</v>
       </c>
       <c r="O89" s="8">
-        <v>66915</v>
+        <v>67003</v>
       </c>
       <c r="P89" s="8">
-        <v>33340</v>
+        <v>33442</v>
       </c>
       <c r="Q89" s="9">
-        <v>94213.9</v>
+        <v>93591.6</v>
       </c>
       <c r="R89" s="9">
-        <v>61370.3</v>
+        <v>60710.1</v>
       </c>
       <c r="S89" s="9">
-        <v>32843.5</v>
+        <v>32881.5</v>
       </c>
       <c r="T89" s="9">
-        <v>44816.9</v>
+        <v>44932.9</v>
       </c>
       <c r="U89" s="9">
-        <v>15722.6</v>
+        <v>15747.7</v>
       </c>
       <c r="V89" s="8">
-        <v>151516</v>
+        <v>151593</v>
       </c>
       <c r="W89" s="8">
-        <v>99237</v>
+        <v>99316</v>
       </c>
       <c r="X89" s="8">
-        <v>52278</v>
+        <v>52277</v>
       </c>
       <c r="Y89" s="8">
-        <v>66319</v>
+        <v>66351</v>
       </c>
       <c r="Z89" s="8">
-        <v>33002</v>
+        <v>33029</v>
       </c>
       <c r="AA89" s="9">
-        <v>91512.2</v>
+        <v>91418.1</v>
       </c>
       <c r="AB89" s="9">
-        <v>60018.400000000001</v>
+        <v>59903.5</v>
       </c>
       <c r="AC89" s="9">
-        <v>31493.8</v>
+        <v>31514.6</v>
       </c>
       <c r="AD89" s="9">
-        <v>44133.599999999999</v>
+        <v>44171.3</v>
       </c>
       <c r="AE89" s="9">
-        <v>15724.8</v>
+        <v>15734.1</v>
       </c>
     </row>
     <row r="90" spans="1:31" x14ac:dyDescent="0.2">
@@ -9313,64 +9313,64 @@
         <v>15132</v>
       </c>
       <c r="L90" s="8">
-        <v>142587</v>
+        <v>142698</v>
       </c>
       <c r="M90" s="8">
-        <v>93606</v>
+        <v>93662</v>
       </c>
       <c r="N90" s="8">
-        <v>48980</v>
+        <v>49036</v>
       </c>
       <c r="O90" s="8">
-        <v>62278</v>
+        <v>62289</v>
       </c>
       <c r="P90" s="8">
-        <v>30812</v>
+        <v>30806</v>
       </c>
       <c r="Q90" s="9">
-        <v>85605.7</v>
+        <v>86514.6</v>
       </c>
       <c r="R90" s="9">
-        <v>56255.9</v>
+        <v>57110.3</v>
       </c>
       <c r="S90" s="9">
-        <v>29349.8</v>
+        <v>29404.3</v>
       </c>
       <c r="T90" s="9">
-        <v>41896.6</v>
+        <v>41933</v>
       </c>
       <c r="U90" s="9">
-        <v>14950</v>
+        <v>14969.1</v>
       </c>
       <c r="V90" s="8">
-        <v>142038</v>
+        <v>142075</v>
       </c>
       <c r="W90" s="8">
-        <v>93223</v>
+        <v>93240</v>
       </c>
       <c r="X90" s="8">
-        <v>48815</v>
+        <v>48834</v>
       </c>
       <c r="Y90" s="8">
-        <v>62304</v>
+        <v>62311</v>
       </c>
       <c r="Z90" s="8">
-        <v>30781</v>
+        <v>30787</v>
       </c>
       <c r="AA90" s="9">
-        <v>85817.2</v>
+        <v>85999.3</v>
       </c>
       <c r="AB90" s="9">
-        <v>56378.7</v>
+        <v>56544.3</v>
       </c>
       <c r="AC90" s="9">
-        <v>29438.5</v>
+        <v>29455.1</v>
       </c>
       <c r="AD90" s="9">
-        <v>41630.9</v>
+        <v>41650</v>
       </c>
       <c r="AE90" s="9">
-        <v>14845</v>
+        <v>14851.5</v>
       </c>
     </row>
     <row r="91" spans="1:31" x14ac:dyDescent="0.2">
@@ -9408,64 +9408,64 @@
         <v>13709</v>
       </c>
       <c r="L91" s="8">
-        <v>129412</v>
+        <v>129252</v>
       </c>
       <c r="M91" s="8">
-        <v>86187</v>
+        <v>86017</v>
       </c>
       <c r="N91" s="8">
-        <v>43226</v>
+        <v>43236</v>
       </c>
       <c r="O91" s="8">
-        <v>57480</v>
+        <v>57455</v>
       </c>
       <c r="P91" s="8">
-        <v>28799</v>
+        <v>28778</v>
       </c>
       <c r="Q91" s="9">
-        <v>76738.8</v>
+        <v>76869.2</v>
       </c>
       <c r="R91" s="9">
-        <v>51296.2</v>
+        <v>51461.8</v>
       </c>
       <c r="S91" s="9">
-        <v>25442.6</v>
+        <v>25407.5</v>
       </c>
       <c r="T91" s="9">
-        <v>37730.5</v>
+        <v>37681.4</v>
       </c>
       <c r="U91" s="9">
-        <v>13975.6</v>
+        <v>13959.1</v>
       </c>
       <c r="V91" s="8">
-        <v>129163</v>
+        <v>129097</v>
       </c>
       <c r="W91" s="8">
-        <v>85466</v>
+        <v>85398</v>
       </c>
       <c r="X91" s="8">
-        <v>43697</v>
+        <v>43699</v>
       </c>
       <c r="Y91" s="8">
-        <v>56728</v>
+        <v>56700</v>
       </c>
       <c r="Z91" s="8">
-        <v>28418</v>
+        <v>28401</v>
       </c>
       <c r="AA91" s="9">
-        <v>77278.899999999994</v>
+        <v>77343.600000000006</v>
       </c>
       <c r="AB91" s="9">
-        <v>51243.4</v>
+        <v>51322.9</v>
       </c>
       <c r="AC91" s="9">
-        <v>26035.5</v>
+        <v>26020.7</v>
       </c>
       <c r="AD91" s="9">
-        <v>37594.9</v>
+        <v>37570.6</v>
       </c>
       <c r="AE91" s="9">
-        <v>13759.7</v>
+        <v>13751.6</v>
       </c>
     </row>
     <row r="92" spans="1:31" x14ac:dyDescent="0.2">
@@ -9503,64 +9503,64 @@
         <v>13798</v>
       </c>
       <c r="L92" s="8">
-        <v>116401</v>
+        <v>116189</v>
       </c>
       <c r="M92" s="8">
-        <v>77026</v>
+        <v>76858</v>
       </c>
       <c r="N92" s="8">
-        <v>39376</v>
+        <v>39331</v>
       </c>
       <c r="O92" s="8">
-        <v>50756</v>
+        <v>50644</v>
       </c>
       <c r="P92" s="8">
-        <v>26160</v>
+        <v>26075</v>
       </c>
       <c r="Q92" s="9">
-        <v>69351.100000000006</v>
+        <v>68804.2</v>
       </c>
       <c r="R92" s="9">
-        <v>46175.8</v>
+        <v>45690.7</v>
       </c>
       <c r="S92" s="9">
-        <v>23175.4</v>
+        <v>23113.599999999999</v>
       </c>
       <c r="T92" s="9">
-        <v>33016.400000000001</v>
+        <v>32915.300000000003</v>
       </c>
       <c r="U92" s="9">
-        <v>12734</v>
+        <v>12704.7</v>
       </c>
       <c r="V92" s="8">
-        <v>117436</v>
+        <v>117407</v>
       </c>
       <c r="W92" s="8">
-        <v>77979</v>
+        <v>77966</v>
       </c>
       <c r="X92" s="8">
-        <v>39457</v>
+        <v>39441</v>
       </c>
       <c r="Y92" s="8">
-        <v>51478</v>
+        <v>51468</v>
       </c>
       <c r="Z92" s="8">
-        <v>26793</v>
+        <v>26791</v>
       </c>
       <c r="AA92" s="9">
-        <v>69945.8</v>
+        <v>69793.899999999994</v>
       </c>
       <c r="AB92" s="9">
-        <v>46614.1</v>
+        <v>46474.6</v>
       </c>
       <c r="AC92" s="9">
-        <v>23331.599999999999</v>
+        <v>23319.3</v>
       </c>
       <c r="AD92" s="9">
-        <v>33492.5</v>
+        <v>33476.800000000003</v>
       </c>
       <c r="AE92" s="9">
-        <v>12971.8</v>
+        <v>12965.5</v>
       </c>
     </row>
     <row r="93" spans="1:31" x14ac:dyDescent="0.2">
@@ -9598,64 +9598,64 @@
         <v>11582.3</v>
       </c>
       <c r="L93" s="8">
-        <v>109727</v>
+        <v>110021</v>
       </c>
       <c r="M93" s="8">
-        <v>72907</v>
+        <v>73237</v>
       </c>
       <c r="N93" s="8">
-        <v>36819</v>
+        <v>36784</v>
       </c>
       <c r="O93" s="8">
-        <v>47317</v>
+        <v>47458</v>
       </c>
       <c r="P93" s="8">
-        <v>26441</v>
+        <v>26586</v>
       </c>
       <c r="Q93" s="9">
-        <v>66158.7</v>
+        <v>65753.7</v>
       </c>
       <c r="R93" s="9">
-        <v>43700.2</v>
+        <v>43249.599999999999</v>
       </c>
       <c r="S93" s="9">
-        <v>22458.6</v>
+        <v>22504.1</v>
       </c>
       <c r="T93" s="9">
-        <v>30622.6</v>
+        <v>30749</v>
       </c>
       <c r="U93" s="9">
-        <v>12646</v>
+        <v>12669.4</v>
       </c>
       <c r="V93" s="8">
-        <v>111219</v>
+        <v>111316</v>
       </c>
       <c r="W93" s="8">
-        <v>73556</v>
+        <v>73659</v>
       </c>
       <c r="X93" s="8">
-        <v>37662</v>
+        <v>37657</v>
       </c>
       <c r="Y93" s="8">
-        <v>48425</v>
+        <v>48471</v>
       </c>
       <c r="Z93" s="8">
-        <v>26684</v>
+        <v>26722</v>
       </c>
       <c r="AA93" s="9">
-        <v>66750.899999999994</v>
+        <v>66484.600000000006</v>
       </c>
       <c r="AB93" s="9">
-        <v>44311.1</v>
+        <v>44023.3</v>
       </c>
       <c r="AC93" s="9">
-        <v>22439.8</v>
+        <v>22461.200000000001</v>
       </c>
       <c r="AD93" s="9">
-        <v>31035.4</v>
+        <v>31073.7</v>
       </c>
       <c r="AE93" s="9">
-        <v>13036.5</v>
+        <v>13049.1</v>
       </c>
     </row>
     <row r="94" spans="1:31" x14ac:dyDescent="0.2">
@@ -9693,64 +9693,64 @@
         <v>14270</v>
       </c>
       <c r="L94" s="8">
-        <v>116406</v>
+        <v>116594</v>
       </c>
       <c r="M94" s="8">
-        <v>77474</v>
+        <v>77576</v>
       </c>
       <c r="N94" s="8">
-        <v>38932</v>
+        <v>39018</v>
       </c>
       <c r="O94" s="8">
-        <v>48927</v>
+        <v>48981</v>
       </c>
       <c r="P94" s="8">
-        <v>27972</v>
+        <v>27970</v>
       </c>
       <c r="Q94" s="9">
-        <v>67150.5</v>
+        <v>68173.399999999994</v>
       </c>
       <c r="R94" s="9">
-        <v>44259.9</v>
+        <v>45198.2</v>
       </c>
       <c r="S94" s="9">
-        <v>22890.6</v>
+        <v>22975.200000000001</v>
       </c>
       <c r="T94" s="9">
-        <v>30825.7</v>
+        <v>30884.7</v>
       </c>
       <c r="U94" s="9">
-        <v>14089.4</v>
+        <v>14130.9</v>
       </c>
       <c r="V94" s="8">
-        <v>111288</v>
+        <v>111323</v>
       </c>
       <c r="W94" s="8">
-        <v>73177</v>
+        <v>73189</v>
       </c>
       <c r="X94" s="8">
-        <v>38111</v>
+        <v>38133</v>
       </c>
       <c r="Y94" s="8">
-        <v>47789</v>
+        <v>47804</v>
       </c>
       <c r="Z94" s="8">
-        <v>27806</v>
+        <v>27811</v>
       </c>
       <c r="AA94" s="9">
-        <v>66808.800000000003</v>
+        <v>67001.100000000006</v>
       </c>
       <c r="AB94" s="9">
-        <v>43810.1</v>
+        <v>43985.4</v>
       </c>
       <c r="AC94" s="9">
-        <v>22998.7</v>
+        <v>23015.7</v>
       </c>
       <c r="AD94" s="9">
-        <v>30553.7</v>
+        <v>30571.1</v>
       </c>
       <c r="AE94" s="9">
-        <v>13826.9</v>
+        <v>13837.3</v>
       </c>
     </row>
     <row r="95" spans="1:31" x14ac:dyDescent="0.2">
@@ -9788,64 +9788,64 @@
         <v>13576.8</v>
       </c>
       <c r="L95" s="8">
-        <v>115729</v>
+        <v>115456</v>
       </c>
       <c r="M95" s="8">
-        <v>75791</v>
+        <v>75533</v>
       </c>
       <c r="N95" s="8">
-        <v>39938</v>
+        <v>39924</v>
       </c>
       <c r="O95" s="8">
-        <v>48417</v>
+        <v>48355</v>
       </c>
       <c r="P95" s="8">
-        <v>27046</v>
+        <v>27005</v>
       </c>
       <c r="Q95" s="9">
-        <v>69395.3</v>
+        <v>69321.2</v>
       </c>
       <c r="R95" s="9">
-        <v>44906.5</v>
+        <v>44902.7</v>
       </c>
       <c r="S95" s="9">
-        <v>24488.799999999999</v>
+        <v>24418.5</v>
       </c>
       <c r="T95" s="9">
-        <v>31400.9</v>
+        <v>31324.6</v>
       </c>
       <c r="U95" s="9">
-        <v>13607.2</v>
+        <v>13582.4</v>
       </c>
       <c r="V95" s="8">
-        <v>116081</v>
+        <v>115971</v>
       </c>
       <c r="W95" s="8">
-        <v>75763</v>
+        <v>75657</v>
       </c>
       <c r="X95" s="8">
-        <v>40318</v>
+        <v>40314</v>
       </c>
       <c r="Y95" s="8">
-        <v>48781</v>
+        <v>48739</v>
       </c>
       <c r="Z95" s="8">
-        <v>28833</v>
+        <v>28801</v>
       </c>
       <c r="AA95" s="9">
-        <v>68732.399999999994</v>
+        <v>70104.100000000006</v>
       </c>
       <c r="AB95" s="9">
-        <v>44288.6</v>
+        <v>45691.4</v>
       </c>
       <c r="AC95" s="9">
-        <v>24443.9</v>
+        <v>24412.7</v>
       </c>
       <c r="AD95" s="9">
-        <v>31537.1</v>
+        <v>31500.3</v>
       </c>
       <c r="AE95" s="9">
-        <v>14742.6</v>
+        <v>14728.3</v>
       </c>
     </row>
     <row r="96" spans="1:31" x14ac:dyDescent="0.2">
@@ -9883,64 +9883,64 @@
         <v>16223.2</v>
       </c>
       <c r="L96" s="8">
-        <v>122574</v>
+        <v>122279</v>
       </c>
       <c r="M96" s="8">
-        <v>79393</v>
+        <v>79121</v>
       </c>
       <c r="N96" s="8">
-        <v>43181</v>
+        <v>43158</v>
       </c>
       <c r="O96" s="8">
-        <v>50003</v>
+        <v>49814</v>
       </c>
       <c r="P96" s="8">
-        <v>29359</v>
+        <v>29230</v>
       </c>
       <c r="Q96" s="9">
-        <v>75338.399999999994</v>
+        <v>74584.600000000006</v>
       </c>
       <c r="R96" s="9">
-        <v>48693.1</v>
+        <v>48030.3</v>
       </c>
       <c r="S96" s="9">
-        <v>26645.4</v>
+        <v>26554.400000000001</v>
       </c>
       <c r="T96" s="9">
-        <v>33190.800000000003</v>
+        <v>33055.1</v>
       </c>
       <c r="U96" s="9">
-        <v>15071.5</v>
+        <v>15019.2</v>
       </c>
       <c r="V96" s="8">
-        <v>122800</v>
+        <v>122768</v>
       </c>
       <c r="W96" s="8">
-        <v>79159</v>
+        <v>79154</v>
       </c>
       <c r="X96" s="8">
-        <v>43640</v>
+        <v>43614</v>
       </c>
       <c r="Y96" s="8">
-        <v>50189</v>
+        <v>50172</v>
       </c>
       <c r="Z96" s="8">
-        <v>29137</v>
+        <v>29128</v>
       </c>
       <c r="AA96" s="9">
-        <v>71964.800000000003</v>
+        <v>74652.399999999994</v>
       </c>
       <c r="AB96" s="9">
-        <v>45558.8</v>
+        <v>48264.7</v>
       </c>
       <c r="AC96" s="9">
-        <v>26406.1</v>
+        <v>26387.7</v>
       </c>
       <c r="AD96" s="9">
-        <v>33103.4</v>
+        <v>33089.5</v>
       </c>
       <c r="AE96" s="9">
-        <v>15378.1</v>
+        <v>15364.8</v>
       </c>
     </row>
     <row r="97" spans="1:31" x14ac:dyDescent="0.2">
@@ -9978,64 +9978,64 @@
         <v>13429.9</v>
       </c>
       <c r="L97" s="8">
-        <v>120526</v>
+        <v>120937</v>
       </c>
       <c r="M97" s="8">
-        <v>76327</v>
+        <v>76841</v>
       </c>
       <c r="N97" s="8">
-        <v>44200</v>
+        <v>44096</v>
       </c>
       <c r="O97" s="8">
-        <v>48719</v>
+        <v>48945</v>
       </c>
       <c r="P97" s="8">
-        <v>28313</v>
+        <v>28520</v>
       </c>
       <c r="Q97" s="9">
-        <v>76064</v>
+        <v>75717.600000000006</v>
       </c>
       <c r="R97" s="9">
-        <v>47695.4</v>
+        <v>47285</v>
       </c>
       <c r="S97" s="9">
-        <v>28368.6</v>
+        <v>28432.6</v>
       </c>
       <c r="T97" s="9">
-        <v>32502</v>
+        <v>32670.9</v>
       </c>
       <c r="U97" s="9">
-        <v>14381.9</v>
+        <v>14407.8</v>
       </c>
       <c r="V97" s="8">
-        <v>129198</v>
+        <v>129361</v>
       </c>
       <c r="W97" s="8">
-        <v>81948</v>
+        <v>82124</v>
       </c>
       <c r="X97" s="8">
-        <v>47250</v>
+        <v>47237</v>
       </c>
       <c r="Y97" s="8">
-        <v>51644</v>
+        <v>51723</v>
       </c>
       <c r="Z97" s="8">
-        <v>29181</v>
+        <v>29236</v>
       </c>
       <c r="AA97" s="9">
-        <v>76768.7</v>
+        <v>79808.2</v>
       </c>
       <c r="AB97" s="9">
-        <v>47923.7</v>
+        <v>50921.2</v>
       </c>
       <c r="AC97" s="9">
-        <v>28845.1</v>
+        <v>28887.1</v>
       </c>
       <c r="AD97" s="9">
-        <v>34822.1</v>
+        <v>34886.400000000001</v>
       </c>
       <c r="AE97" s="9">
-        <v>15765.7</v>
+        <v>15783.2</v>
       </c>
     </row>
     <row r="98" spans="1:31" x14ac:dyDescent="0.2">
@@ -10073,64 +10073,64 @@
         <v>16357</v>
       </c>
       <c r="L98" s="8">
-        <v>133513</v>
+        <v>133859</v>
       </c>
       <c r="M98" s="8">
-        <v>83566</v>
+        <v>83739</v>
       </c>
       <c r="N98" s="8">
-        <v>49947</v>
+        <v>50120</v>
       </c>
       <c r="O98" s="8">
-        <v>52889</v>
+        <v>52998</v>
       </c>
       <c r="P98" s="8">
-        <v>29897</v>
+        <v>29912</v>
       </c>
       <c r="Q98" s="9">
-        <v>82799.899999999994</v>
+        <v>84315.9</v>
       </c>
       <c r="R98" s="9">
-        <v>51591</v>
+        <v>52931.1</v>
       </c>
       <c r="S98" s="9">
-        <v>31208.9</v>
+        <v>31384.9</v>
       </c>
       <c r="T98" s="9">
-        <v>36328.1</v>
+        <v>36445.1</v>
       </c>
       <c r="U98" s="9">
-        <v>16167.6</v>
+        <v>16246.9</v>
       </c>
       <c r="V98" s="8">
-        <v>133384</v>
+        <v>133469</v>
       </c>
       <c r="W98" s="8">
-        <v>83541</v>
+        <v>83593</v>
       </c>
       <c r="X98" s="8">
-        <v>49843</v>
+        <v>49875</v>
       </c>
       <c r="Y98" s="8">
-        <v>53066</v>
+        <v>53107</v>
       </c>
       <c r="Z98" s="8">
-        <v>29347</v>
+        <v>29362</v>
       </c>
       <c r="AA98" s="9">
-        <v>82278.7</v>
+        <v>84145</v>
       </c>
       <c r="AB98" s="9">
-        <v>51116.7</v>
+        <v>52947.4</v>
       </c>
       <c r="AC98" s="9">
-        <v>31162</v>
+        <v>31197.599999999999</v>
       </c>
       <c r="AD98" s="9">
-        <v>36563.599999999999</v>
+        <v>36596.9</v>
       </c>
       <c r="AE98" s="9">
-        <v>16034.7</v>
+        <v>16057.4</v>
       </c>
     </row>
     <row r="99" spans="1:31" x14ac:dyDescent="0.2">
@@ -10168,64 +10168,64 @@
         <v>15835.1</v>
       </c>
       <c r="L99" s="8">
-        <v>134601</v>
+        <v>134130</v>
       </c>
       <c r="M99" s="8">
-        <v>83575</v>
+        <v>83165</v>
       </c>
       <c r="N99" s="8">
-        <v>51026</v>
+        <v>50965</v>
       </c>
       <c r="O99" s="8">
-        <v>53635</v>
+        <v>53526</v>
       </c>
       <c r="P99" s="8">
-        <v>29468</v>
+        <v>29395</v>
       </c>
       <c r="Q99" s="9">
-        <v>87253</v>
+        <v>86927.7</v>
       </c>
       <c r="R99" s="9">
-        <v>53705.4</v>
+        <v>53521.7</v>
       </c>
       <c r="S99" s="9">
-        <v>33547.599999999999</v>
+        <v>33406</v>
       </c>
       <c r="T99" s="9">
-        <v>37952</v>
+        <v>37812.5</v>
       </c>
       <c r="U99" s="9">
-        <v>15937.9</v>
+        <v>15899.4</v>
       </c>
       <c r="V99" s="8">
-        <v>133501</v>
+        <v>133350</v>
       </c>
       <c r="W99" s="8">
-        <v>83276</v>
+        <v>83124</v>
       </c>
       <c r="X99" s="8">
-        <v>50225</v>
+        <v>50226</v>
       </c>
       <c r="Y99" s="8">
-        <v>53549</v>
+        <v>53486</v>
       </c>
       <c r="Z99" s="8">
-        <v>29388</v>
+        <v>29348</v>
       </c>
       <c r="AA99" s="9">
-        <v>86101.7</v>
+        <v>86033.3</v>
       </c>
       <c r="AB99" s="9">
-        <v>53574.2</v>
+        <v>53554.2</v>
       </c>
       <c r="AC99" s="9">
-        <v>32527.4</v>
+        <v>32479</v>
       </c>
       <c r="AD99" s="9">
-        <v>37740.6</v>
+        <v>37683.800000000003</v>
       </c>
       <c r="AE99" s="9">
-        <v>16008.6</v>
+        <v>15995.3</v>
       </c>
     </row>
     <row r="100" spans="1:31" x14ac:dyDescent="0.2">
@@ -10263,64 +10263,64 @@
         <v>16819.599999999999</v>
       </c>
       <c r="L100" s="8">
-        <v>131735</v>
+        <v>131392</v>
       </c>
       <c r="M100" s="8">
-        <v>82838</v>
+        <v>82477</v>
       </c>
       <c r="N100" s="8">
-        <v>48897</v>
+        <v>48915</v>
       </c>
       <c r="O100" s="8">
-        <v>54006</v>
+        <v>53721</v>
       </c>
       <c r="P100" s="8">
-        <v>29134</v>
+        <v>28966</v>
       </c>
       <c r="Q100" s="9">
-        <v>87704.2</v>
+        <v>86665.8</v>
       </c>
       <c r="R100" s="9">
-        <v>55084.5</v>
+        <v>54182.9</v>
       </c>
       <c r="S100" s="9">
-        <v>32619.7</v>
+        <v>32482.9</v>
       </c>
       <c r="T100" s="9">
-        <v>38919.199999999997</v>
+        <v>38732.800000000003</v>
       </c>
       <c r="U100" s="9">
-        <v>15777.5</v>
+        <v>15705.6</v>
       </c>
       <c r="V100" s="8">
-        <v>131316</v>
+        <v>131238</v>
       </c>
       <c r="W100" s="8">
-        <v>82181</v>
+        <v>82130</v>
       </c>
       <c r="X100" s="8">
-        <v>49135</v>
+        <v>49109</v>
       </c>
       <c r="Y100" s="8">
-        <v>53303</v>
+        <v>53257</v>
       </c>
       <c r="Z100" s="8">
-        <v>29122</v>
+        <v>29107</v>
       </c>
       <c r="AA100" s="9">
-        <v>87362.1</v>
+        <v>86537.8</v>
       </c>
       <c r="AB100" s="9">
-        <v>54406.7</v>
+        <v>53619.5</v>
       </c>
       <c r="AC100" s="9">
-        <v>32955.300000000003</v>
+        <v>32918.400000000001</v>
       </c>
       <c r="AD100" s="9">
-        <v>38295.300000000003</v>
+        <v>38261.300000000003</v>
       </c>
       <c r="AE100" s="9">
-        <v>15568.9</v>
+        <v>15546.2</v>
       </c>
     </row>
     <row r="101" spans="1:31" x14ac:dyDescent="0.2">
@@ -10358,64 +10358,64 @@
         <v>14128.1</v>
       </c>
       <c r="L101" s="8">
-        <v>128255</v>
+        <v>128732</v>
       </c>
       <c r="M101" s="8">
-        <v>79787</v>
+        <v>80453</v>
       </c>
       <c r="N101" s="8">
-        <v>48468</v>
+        <v>48279</v>
       </c>
       <c r="O101" s="8">
-        <v>52121</v>
+        <v>52432</v>
       </c>
       <c r="P101" s="8">
-        <v>28533</v>
+        <v>28805</v>
       </c>
       <c r="Q101" s="9">
-        <v>87136.5</v>
+        <v>86904.6</v>
       </c>
       <c r="R101" s="9">
-        <v>54070.2</v>
+        <v>53753.4</v>
       </c>
       <c r="S101" s="9">
-        <v>33066.300000000003</v>
+        <v>33151.199999999997</v>
       </c>
       <c r="T101" s="9">
-        <v>38014.199999999997</v>
+        <v>38235.300000000003</v>
       </c>
       <c r="U101" s="9">
-        <v>15168.3</v>
+        <v>15191.9</v>
       </c>
       <c r="V101" s="8">
-        <v>130771</v>
+        <v>130945</v>
       </c>
       <c r="W101" s="8">
-        <v>81655</v>
+        <v>81858</v>
       </c>
       <c r="X101" s="8">
-        <v>49116</v>
+        <v>49087</v>
       </c>
       <c r="Y101" s="8">
-        <v>53079</v>
+        <v>53171</v>
       </c>
       <c r="Z101" s="8">
-        <v>28797</v>
+        <v>28865</v>
       </c>
       <c r="AA101" s="9">
-        <v>88270.5</v>
+        <v>88581.4</v>
       </c>
       <c r="AB101" s="9">
-        <v>54573.9</v>
+        <v>54835</v>
       </c>
       <c r="AC101" s="9">
-        <v>33696.6</v>
+        <v>33746.400000000001</v>
       </c>
       <c r="AD101" s="9">
-        <v>38826.5</v>
+        <v>38902</v>
       </c>
       <c r="AE101" s="9">
-        <v>15148.4</v>
+        <v>15162.3</v>
       </c>
     </row>
     <row r="102" spans="1:31" x14ac:dyDescent="0.2">
@@ -10453,64 +10453,64 @@
         <v>16734.599999999999</v>
       </c>
       <c r="L102" s="8">
-        <v>134566</v>
+        <v>135055</v>
       </c>
       <c r="M102" s="8">
-        <v>83902</v>
+        <v>84151</v>
       </c>
       <c r="N102" s="8">
-        <v>50665</v>
+        <v>50904</v>
       </c>
       <c r="O102" s="8">
-        <v>53751</v>
+        <v>53920</v>
       </c>
       <c r="P102" s="8">
-        <v>29319</v>
+        <v>29335</v>
       </c>
       <c r="Q102" s="9">
-        <v>89147.8</v>
+        <v>91005.1</v>
       </c>
       <c r="R102" s="9">
-        <v>55598.2</v>
+        <v>57206.7</v>
       </c>
       <c r="S102" s="9">
-        <v>33549.599999999999</v>
+        <v>33798.400000000001</v>
       </c>
       <c r="T102" s="9">
-        <v>40105.199999999997</v>
+        <v>40285.1</v>
       </c>
       <c r="U102" s="9">
-        <v>16578.3</v>
+        <v>16686.2</v>
       </c>
       <c r="V102" s="8">
-        <v>134881</v>
+        <v>135491</v>
       </c>
       <c r="W102" s="8">
-        <v>83031</v>
+        <v>83462</v>
       </c>
       <c r="X102" s="8">
-        <v>51850</v>
+        <v>52030</v>
       </c>
       <c r="Y102" s="8">
-        <v>53779</v>
+        <v>54059</v>
       </c>
       <c r="Z102" s="8">
-        <v>29243</v>
+        <v>29333</v>
       </c>
       <c r="AA102" s="9">
-        <v>92420.2</v>
+        <v>94249.600000000006</v>
       </c>
       <c r="AB102" s="9">
-        <v>56311.7</v>
+        <v>57975.199999999997</v>
       </c>
       <c r="AC102" s="9">
-        <v>36108.5</v>
+        <v>36274.400000000001</v>
       </c>
       <c r="AD102" s="9">
-        <v>40310.300000000003</v>
+        <v>40525.199999999997</v>
       </c>
       <c r="AE102" s="9">
-        <v>15627.9</v>
+        <v>15675.3</v>
       </c>
     </row>
     <row r="103" spans="1:31" x14ac:dyDescent="0.2">
@@ -10548,64 +10548,64 @@
         <v>16388.400000000001</v>
       </c>
       <c r="L103" s="8">
-        <v>142216</v>
+        <v>141555</v>
       </c>
       <c r="M103" s="8">
-        <v>84947</v>
+        <v>84423</v>
       </c>
       <c r="N103" s="8">
-        <v>57269</v>
+        <v>57133</v>
       </c>
       <c r="O103" s="8">
-        <v>55274</v>
+        <v>55107</v>
       </c>
       <c r="P103" s="8">
-        <v>29772</v>
+        <v>29675</v>
       </c>
       <c r="Q103" s="9">
-        <v>98887.2</v>
+        <v>98259.8</v>
       </c>
       <c r="R103" s="9">
-        <v>59064.9</v>
+        <v>58674.3</v>
       </c>
       <c r="S103" s="9">
-        <v>39822.300000000003</v>
+        <v>39585.5</v>
       </c>
       <c r="T103" s="9">
-        <v>42725.9</v>
+        <v>42518.3</v>
       </c>
       <c r="U103" s="9">
-        <v>16714.8</v>
+        <v>16671</v>
       </c>
       <c r="V103" s="8">
-        <v>141599</v>
+        <v>141186</v>
       </c>
       <c r="W103" s="8">
-        <v>85547</v>
+        <v>85214</v>
       </c>
       <c r="X103" s="8">
-        <v>56052</v>
+        <v>55972</v>
       </c>
       <c r="Y103" s="8">
-        <v>55251</v>
+        <v>55092</v>
       </c>
       <c r="Z103" s="8">
-        <v>30157</v>
+        <v>30068</v>
       </c>
       <c r="AA103" s="9">
-        <v>99118.7</v>
+        <v>100501.7</v>
       </c>
       <c r="AB103" s="9">
-        <v>59675.1</v>
+        <v>61176.3</v>
       </c>
       <c r="AC103" s="9">
-        <v>39443.599999999999</v>
+        <v>39325.5</v>
       </c>
       <c r="AD103" s="9">
-        <v>42614.400000000001</v>
+        <v>42479.199999999997</v>
       </c>
       <c r="AE103" s="9">
-        <v>16904</v>
+        <v>16871.3</v>
       </c>
     </row>
     <row r="104" spans="1:31" x14ac:dyDescent="0.2">
@@ -10643,64 +10643,159 @@
         <v>20667.099999999999</v>
       </c>
       <c r="L104" s="8">
-        <v>149434</v>
+        <v>149066</v>
       </c>
       <c r="M104" s="8">
-        <v>88990</v>
+        <v>88537</v>
       </c>
       <c r="N104" s="8">
-        <v>60445</v>
+        <v>60529</v>
       </c>
       <c r="O104" s="8">
-        <v>57282</v>
+        <v>56936</v>
       </c>
       <c r="P104" s="8">
-        <v>31783</v>
+        <v>31590</v>
       </c>
       <c r="Q104" s="9">
-        <v>108300.1</v>
+        <v>107006.2</v>
       </c>
       <c r="R104" s="9">
-        <v>65315</v>
+        <v>64184.1</v>
       </c>
       <c r="S104" s="9">
-        <v>42985</v>
+        <v>42822.1</v>
       </c>
       <c r="T104" s="9">
-        <v>45500.800000000003</v>
+        <v>45271.7</v>
       </c>
       <c r="U104" s="9">
-        <v>19309.599999999999</v>
+        <v>19206.599999999999</v>
       </c>
       <c r="V104" s="8">
-        <v>149199</v>
+        <v>144299</v>
       </c>
       <c r="W104" s="8">
-        <v>88586</v>
+        <v>85710</v>
       </c>
       <c r="X104" s="8">
-        <v>60613</v>
+        <v>58588</v>
       </c>
       <c r="Y104" s="8">
-        <v>57046</v>
+        <v>55382</v>
       </c>
       <c r="Z104" s="8">
-        <v>31344</v>
+        <v>30633</v>
       </c>
       <c r="AA104" s="9">
-        <v>106978.5</v>
+        <v>104508.9</v>
       </c>
       <c r="AB104" s="9">
-        <v>64022.400000000001</v>
+        <v>62978.400000000001</v>
       </c>
       <c r="AC104" s="9">
-        <v>42956.1</v>
+        <v>41530.400000000001</v>
       </c>
       <c r="AD104" s="9">
-        <v>45311.7</v>
+        <v>43838.1</v>
       </c>
       <c r="AE104" s="9">
-        <v>18662</v>
+        <v>18024.900000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A105" s="10">
+        <v>46082</v>
+      </c>
+      <c r="B105" s="8">
+        <v>127480</v>
+      </c>
+      <c r="C105" s="8">
+        <v>75766</v>
+      </c>
+      <c r="D105" s="8">
+        <v>51714</v>
+      </c>
+      <c r="E105" s="8">
+        <v>48688</v>
+      </c>
+      <c r="F105" s="8">
+        <v>27078</v>
+      </c>
+      <c r="G105" s="9">
+        <v>92348.4</v>
+      </c>
+      <c r="H105" s="9">
+        <v>55679</v>
+      </c>
+      <c r="I105" s="9">
+        <v>36669.5</v>
+      </c>
+      <c r="J105" s="9">
+        <v>39051.800000000003</v>
+      </c>
+      <c r="K105" s="9">
+        <v>16627.2</v>
+      </c>
+      <c r="L105" s="8">
+        <v>139794</v>
+      </c>
+      <c r="M105" s="8">
+        <v>82453</v>
+      </c>
+      <c r="N105" s="8">
+        <v>57342</v>
+      </c>
+      <c r="O105" s="8">
+        <v>53265</v>
+      </c>
+      <c r="P105" s="8">
+        <v>30241</v>
+      </c>
+      <c r="Q105" s="9">
+        <v>102959.2</v>
+      </c>
+      <c r="R105" s="9">
+        <v>61421.599999999999</v>
+      </c>
+      <c r="S105" s="9">
+        <v>41537.599999999999</v>
+      </c>
+      <c r="T105" s="9">
+        <v>43021.8</v>
+      </c>
+      <c r="U105" s="9">
+        <v>17913.900000000001</v>
+      </c>
+      <c r="V105" s="8">
+        <v>144793</v>
+      </c>
+      <c r="W105" s="8">
+        <v>84907</v>
+      </c>
+      <c r="X105" s="8">
+        <v>59886</v>
+      </c>
+      <c r="Y105" s="8">
+        <v>54858</v>
+      </c>
+      <c r="Z105" s="8">
+        <v>30954</v>
+      </c>
+      <c r="AA105" s="9">
+        <v>106428.3</v>
+      </c>
+      <c r="AB105" s="9">
+        <v>63466.7</v>
+      </c>
+      <c r="AC105" s="9">
+        <v>42961.5</v>
+      </c>
+      <c r="AD105" s="9">
+        <v>44463.5</v>
+      </c>
+      <c r="AE105" s="9">
+        <v>18896.400000000001</v>
       </c>
     </row>
   </sheetData>
